--- a/research/traditional_assets/database/data/mauritius/mauritius_apparel.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_apparel.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1020053951511319</v>
+        <v>0.1018906370584052</v>
       </c>
       <c r="C2">
-        <v>688.0821272579019</v>
+        <v>681.4671532743291</v>
       </c>
       <c r="D2">
-        <v>412.2821272579019</v>
+        <v>412.4511532743291</v>
       </c>
       <c r="E2">
-        <v>-340.9</v>
+        <v>-334.116</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.784</v>
       </c>
       <c r="G2">
         <v>275.8</v>
@@ -1439,28 +1439,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3412352</v>
       </c>
       <c r="N2">
-        <v>127.5469387755102</v>
+        <v>127.2057035755102</v>
       </c>
       <c r="O2">
-        <v>19.13204081632653</v>
+        <v>19.08085553632653</v>
       </c>
       <c r="P2">
-        <v>108.4148979591837</v>
+        <v>108.1248480391837</v>
       </c>
       <c r="Q2">
-        <v>143.2148979591837</v>
+        <v>142.9248480391837</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1020053951511319</v>
+        <v>0.1024879667256618</v>
       </c>
       <c r="T2">
-        <v>0.7736884202461266</v>
+        <v>0.7803311996118761</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>373.7801339823976</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1018906370584052</v>
+        <v>0.1017758789656786</v>
       </c>
       <c r="C3">
-        <v>681.4671532743291</v>
+        <v>674.8523179410158</v>
       </c>
       <c r="D3">
-        <v>412.4511532743291</v>
+        <v>412.6203179410157</v>
       </c>
       <c r="E3">
-        <v>-334.116</v>
+        <v>-327.332</v>
       </c>
       <c r="F3">
-        <v>6.784</v>
+        <v>13.568</v>
       </c>
       <c r="G3">
         <v>275.8</v>
@@ -1521,28 +1521,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M3">
-        <v>0.3412352</v>
+        <v>0.6824703999999999</v>
       </c>
       <c r="N3">
-        <v>127.2057035755102</v>
+        <v>126.8644683755102</v>
       </c>
       <c r="O3">
-        <v>19.08085553632653</v>
+        <v>19.02967025632653</v>
       </c>
       <c r="P3">
-        <v>108.1248480391837</v>
+        <v>107.8347981191837</v>
       </c>
       <c r="Q3">
-        <v>142.9248480391837</v>
+        <v>142.6347981191837</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1024879667256618</v>
+        <v>0.102980386699672</v>
       </c>
       <c r="T3">
-        <v>0.7803311996118761</v>
+        <v>0.7871095459034575</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>373.7801339823976</v>
+        <v>186.8900669911988</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1017758789656786</v>
+        <v>0.1016611208729518</v>
       </c>
       <c r="C4">
-        <v>674.8523179410158</v>
+        <v>668.237621428632</v>
       </c>
       <c r="D4">
-        <v>412.6203179410157</v>
+        <v>412.789621428632</v>
       </c>
       <c r="E4">
-        <v>-327.332</v>
+        <v>-320.548</v>
       </c>
       <c r="F4">
-        <v>13.568</v>
+        <v>20.352</v>
       </c>
       <c r="G4">
         <v>275.8</v>
@@ -1603,28 +1603,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M4">
-        <v>0.6824703999999999</v>
+        <v>1.0237056</v>
       </c>
       <c r="N4">
-        <v>126.8644683755102</v>
+        <v>126.5232331755102</v>
       </c>
       <c r="O4">
-        <v>19.02967025632653</v>
+        <v>18.97848497632653</v>
       </c>
       <c r="P4">
-        <v>107.8347981191837</v>
+        <v>107.5447481991837</v>
       </c>
       <c r="Q4">
-        <v>142.6347981191837</v>
+        <v>142.3447481991837</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.102980386699672</v>
+        <v>0.1034829596628369</v>
       </c>
       <c r="T4">
-        <v>0.7871095459034575</v>
+        <v>0.7940276519123907</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>186.8900669911988</v>
+        <v>124.5933779941325</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1016611208729518</v>
+        <v>0.1015463627802251</v>
       </c>
       <c r="C5">
-        <v>668.237621428632</v>
+        <v>661.6230639081282</v>
       </c>
       <c r="D5">
-        <v>412.789621428632</v>
+        <v>412.9590639081281</v>
       </c>
       <c r="E5">
-        <v>-320.548</v>
+        <v>-313.764</v>
       </c>
       <c r="F5">
-        <v>20.352</v>
+        <v>27.136</v>
       </c>
       <c r="G5">
         <v>275.8</v>
@@ -1685,28 +1685,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M5">
-        <v>1.0237056</v>
+        <v>1.3649408</v>
       </c>
       <c r="N5">
-        <v>126.5232331755102</v>
+        <v>126.1819979755102</v>
       </c>
       <c r="O5">
-        <v>18.97848497632653</v>
+        <v>18.92729969632653</v>
       </c>
       <c r="P5">
-        <v>107.5447481991837</v>
+        <v>107.2546982791837</v>
       </c>
       <c r="Q5">
-        <v>142.3447481991837</v>
+        <v>142.0546982791837</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1034829596628369</v>
+        <v>0.1039960028960679</v>
       </c>
       <c r="T5">
-        <v>0.7940276519123907</v>
+        <v>0.8010898851298436</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>124.5933779941325</v>
+        <v>93.44503349559939</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1015463627802251</v>
+        <v>0.1014316046874984</v>
       </c>
       <c r="C6">
-        <v>661.6230639081282</v>
+        <v>655.0086455507352</v>
       </c>
       <c r="D6">
-        <v>412.9590639081281</v>
+        <v>413.1286455507351</v>
       </c>
       <c r="E6">
-        <v>-313.764</v>
+        <v>-306.98</v>
       </c>
       <c r="F6">
-        <v>27.136</v>
+        <v>33.92</v>
       </c>
       <c r="G6">
         <v>275.8</v>
@@ -1767,28 +1767,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M6">
-        <v>1.3649408</v>
+        <v>1.706176</v>
       </c>
       <c r="N6">
-        <v>126.1819979755102</v>
+        <v>125.8407627755102</v>
       </c>
       <c r="O6">
-        <v>18.92729969632653</v>
+        <v>18.87611441632653</v>
       </c>
       <c r="P6">
-        <v>107.2546982791837</v>
+        <v>106.9646483591837</v>
       </c>
       <c r="Q6">
-        <v>142.0546982791837</v>
+        <v>141.7646483591837</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1039960028960679</v>
+        <v>0.104519847039472</v>
       </c>
       <c r="T6">
-        <v>0.8010898851298436</v>
+        <v>0.808300796941348</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>93.44503349559939</v>
+        <v>74.7560267964795</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1014316046874984</v>
+        <v>0.1013168465947717</v>
       </c>
       <c r="C7">
-        <v>655.0086455507352</v>
+        <v>648.3943665279653</v>
       </c>
       <c r="D7">
-        <v>413.1286455507351</v>
+        <v>413.2983665279653</v>
       </c>
       <c r="E7">
-        <v>-306.98</v>
+        <v>-300.196</v>
       </c>
       <c r="F7">
-        <v>33.92</v>
+        <v>40.704</v>
       </c>
       <c r="G7">
         <v>275.8</v>
@@ -1849,28 +1849,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M7">
-        <v>1.706176</v>
+        <v>2.0474112</v>
       </c>
       <c r="N7">
-        <v>125.8407627755102</v>
+        <v>125.4995275755102</v>
       </c>
       <c r="O7">
-        <v>18.87611441632653</v>
+        <v>18.82492913632653</v>
       </c>
       <c r="P7">
-        <v>106.9646483591837</v>
+        <v>106.6745984391837</v>
       </c>
       <c r="Q7">
-        <v>141.7646483591837</v>
+        <v>141.4745984391837</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.104519847039472</v>
+        <v>0.1050548368029487</v>
       </c>
       <c r="T7">
-        <v>0.808300796941348</v>
+        <v>0.8156651324084164</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>74.7560267964795</v>
+        <v>62.29668899706625</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1013168465947717</v>
+        <v>0.1012020885020451</v>
       </c>
       <c r="C8">
-        <v>648.3943665279653</v>
+        <v>641.7802270116133</v>
       </c>
       <c r="D8">
-        <v>413.2983665279653</v>
+        <v>413.4682270116132</v>
       </c>
       <c r="E8">
-        <v>-300.196</v>
+        <v>-293.412</v>
       </c>
       <c r="F8">
-        <v>40.704</v>
+        <v>47.48799999999999</v>
       </c>
       <c r="G8">
         <v>275.8</v>
@@ -1931,28 +1931,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M8">
-        <v>2.0474112</v>
+        <v>2.388646399999999</v>
       </c>
       <c r="N8">
-        <v>125.4995275755102</v>
+        <v>125.1582923755102</v>
       </c>
       <c r="O8">
-        <v>18.82492913632653</v>
+        <v>18.77374385632653</v>
       </c>
       <c r="P8">
-        <v>106.6745984391837</v>
+        <v>106.3845485191837</v>
       </c>
       <c r="Q8">
-        <v>141.4745984391837</v>
+        <v>141.1845485191837</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1050548368029487</v>
+        <v>0.1056013317226291</v>
       </c>
       <c r="T8">
-        <v>0.8156651324084164</v>
+        <v>0.8231878406812283</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>62.29668899706625</v>
+        <v>53.39716199748538</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1012020885020451</v>
+        <v>0.1010873304093184</v>
       </c>
       <c r="C9">
-        <v>641.7802270116133</v>
+        <v>635.1662271737558</v>
       </c>
       <c r="D9">
-        <v>413.4682270116132</v>
+        <v>413.6382271737559</v>
       </c>
       <c r="E9">
-        <v>-293.412</v>
+        <v>-286.628</v>
       </c>
       <c r="F9">
-        <v>47.488</v>
+        <v>54.272</v>
       </c>
       <c r="G9">
         <v>275.8</v>
@@ -2013,28 +2013,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M9">
-        <v>2.3886464</v>
+        <v>2.7298816</v>
       </c>
       <c r="N9">
-        <v>125.1582923755102</v>
+        <v>124.8170571755102</v>
       </c>
       <c r="O9">
-        <v>18.77374385632653</v>
+        <v>18.72255857632653</v>
       </c>
       <c r="P9">
-        <v>106.3845485191837</v>
+        <v>106.0944985991837</v>
       </c>
       <c r="Q9">
-        <v>141.1845485191837</v>
+        <v>140.8944985991837</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1056013317226291</v>
+        <v>0.1061597069666504</v>
       </c>
       <c r="T9">
-        <v>0.8231878406812283</v>
+        <v>0.8308740860904056</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>53.39716199748536</v>
+        <v>46.72251674779969</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1010873304093184</v>
+        <v>0.1009725723165917</v>
       </c>
       <c r="C10">
-        <v>635.1662271737558</v>
+        <v>628.5523671867531</v>
       </c>
       <c r="D10">
-        <v>413.6382271737559</v>
+        <v>413.8083671867531</v>
       </c>
       <c r="E10">
-        <v>-286.628</v>
+        <v>-279.844</v>
       </c>
       <c r="F10">
-        <v>54.272</v>
+        <v>61.056</v>
       </c>
       <c r="G10">
         <v>275.8</v>
@@ -2095,28 +2095,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M10">
-        <v>2.7298816</v>
+        <v>3.0711168</v>
       </c>
       <c r="N10">
-        <v>124.8170571755102</v>
+        <v>124.4758219755102</v>
       </c>
       <c r="O10">
-        <v>18.72255857632653</v>
+        <v>18.67137329632653</v>
       </c>
       <c r="P10">
-        <v>106.0944985991837</v>
+        <v>105.8044486791837</v>
       </c>
       <c r="Q10">
-        <v>140.8944985991837</v>
+        <v>140.6044486791837</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1061597069666504</v>
+        <v>0.1067303541940568</v>
       </c>
       <c r="T10">
-        <v>0.8308740860904056</v>
+        <v>0.8387292599701142</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>46.72251674779969</v>
+        <v>41.53112599804417</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1009725723165917</v>
+        <v>0.100857814223865</v>
       </c>
       <c r="C11">
-        <v>628.5523671867531</v>
+        <v>621.9386472232487</v>
       </c>
       <c r="D11">
-        <v>413.8083671867531</v>
+        <v>413.9786472232487</v>
       </c>
       <c r="E11">
-        <v>-279.844</v>
+        <v>-273.06</v>
       </c>
       <c r="F11">
-        <v>61.056</v>
+        <v>67.83999999999999</v>
       </c>
       <c r="G11">
         <v>275.8</v>
@@ -2177,28 +2177,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M11">
-        <v>3.0711168</v>
+        <v>3.412351999999999</v>
       </c>
       <c r="N11">
-        <v>124.4758219755102</v>
+        <v>124.1345867755102</v>
       </c>
       <c r="O11">
-        <v>18.67137329632653</v>
+        <v>18.62018801632653</v>
       </c>
       <c r="P11">
-        <v>105.8044486791837</v>
+        <v>105.5143987591837</v>
       </c>
       <c r="Q11">
-        <v>140.6044486791837</v>
+        <v>140.3143987591837</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1067303541940568</v>
+        <v>0.1073136824709611</v>
       </c>
       <c r="T11">
-        <v>0.8387292599701142</v>
+        <v>0.846758993269372</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>41.53112599804417</v>
+        <v>37.37801339823976</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.100857814223865</v>
+        <v>0.1007430561311383</v>
       </c>
       <c r="C12">
-        <v>621.9386472232487</v>
+        <v>615.3250674561709</v>
       </c>
       <c r="D12">
-        <v>413.9786472232487</v>
+        <v>414.1490674561709</v>
       </c>
       <c r="E12">
-        <v>-273.0599999999999</v>
+        <v>-266.276</v>
       </c>
       <c r="F12">
-        <v>67.84</v>
+        <v>74.624</v>
       </c>
       <c r="G12">
         <v>275.8</v>
@@ -2259,28 +2259,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M12">
-        <v>3.412352</v>
+        <v>3.7535872</v>
       </c>
       <c r="N12">
-        <v>124.1345867755102</v>
+        <v>123.7933515755102</v>
       </c>
       <c r="O12">
-        <v>18.62018801632653</v>
+        <v>18.56900273632653</v>
       </c>
       <c r="P12">
-        <v>105.5143987591837</v>
+        <v>105.2243488391837</v>
       </c>
       <c r="Q12">
-        <v>140.3143987591837</v>
+        <v>140.0243488391837</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1073136824709611</v>
+        <v>0.10791011924847</v>
       </c>
       <c r="T12">
-        <v>0.846758993269372</v>
+        <v>0.8549691700135568</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>37.37801339823975</v>
+        <v>33.98001218021796</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1007430561311383</v>
+        <v>0.1006282980384116</v>
       </c>
       <c r="C13">
-        <v>615.3250674561709</v>
+        <v>608.7116280587323</v>
       </c>
       <c r="D13">
-        <v>414.1490674561709</v>
+        <v>414.3196280587323</v>
       </c>
       <c r="E13">
-        <v>-266.276</v>
+        <v>-259.492</v>
       </c>
       <c r="F13">
-        <v>74.624</v>
+        <v>81.408</v>
       </c>
       <c r="G13">
         <v>275.8</v>
@@ -2341,28 +2341,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M13">
-        <v>3.7535872</v>
+        <v>4.0948224</v>
       </c>
       <c r="N13">
-        <v>123.7933515755102</v>
+        <v>123.4521163755102</v>
       </c>
       <c r="O13">
-        <v>18.56900273632653</v>
+        <v>18.51781745632653</v>
       </c>
       <c r="P13">
-        <v>105.2243488391837</v>
+        <v>104.9342989191837</v>
       </c>
       <c r="Q13">
-        <v>140.0243488391837</v>
+        <v>139.7342989191837</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.10791011924847</v>
+        <v>0.1085201114072859</v>
       </c>
       <c r="T13">
-        <v>0.8549691700135568</v>
+        <v>0.8633659416837459</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>33.98001218021796</v>
+        <v>31.14834449853313</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1006282980384116</v>
+        <v>0.1005135399456849</v>
       </c>
       <c r="C14">
-        <v>608.7116280587323</v>
+        <v>602.0983292044316</v>
       </c>
       <c r="D14">
-        <v>414.3196280587323</v>
+        <v>414.4903292044315</v>
       </c>
       <c r="E14">
-        <v>-259.492</v>
+        <v>-252.708</v>
       </c>
       <c r="F14">
-        <v>81.408</v>
+        <v>88.19199999999999</v>
       </c>
       <c r="G14">
         <v>275.8</v>
@@ -2423,28 +2423,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M14">
-        <v>4.0948224</v>
+        <v>4.4360576</v>
       </c>
       <c r="N14">
-        <v>123.4521163755102</v>
+        <v>123.1108811755102</v>
       </c>
       <c r="O14">
-        <v>18.51781745632653</v>
+        <v>18.46663217632653</v>
       </c>
       <c r="P14">
-        <v>104.9342989191837</v>
+        <v>104.6442489991837</v>
       </c>
       <c r="Q14">
-        <v>139.7342989191837</v>
+        <v>139.4442489991837</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1085201114072859</v>
+        <v>0.1091441263743504</v>
       </c>
       <c r="T14">
-        <v>0.8633659416837459</v>
+        <v>0.8719557425877323</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>31.14834449853313</v>
+        <v>28.75231799864596</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1005135399456849</v>
+        <v>0.1003987818529582</v>
       </c>
       <c r="C15">
-        <v>602.0983292044316</v>
+        <v>595.4851710670529</v>
       </c>
       <c r="D15">
-        <v>414.4903292044315</v>
+        <v>414.6611710670528</v>
       </c>
       <c r="E15">
-        <v>-252.708</v>
+        <v>-245.924</v>
       </c>
       <c r="F15">
-        <v>88.19199999999999</v>
+        <v>94.976</v>
       </c>
       <c r="G15">
         <v>275.8</v>
@@ -2505,28 +2505,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M15">
-        <v>4.4360576</v>
+        <v>4.7772928</v>
       </c>
       <c r="N15">
-        <v>123.1108811755102</v>
+        <v>122.7696459755102</v>
       </c>
       <c r="O15">
-        <v>18.46663217632653</v>
+        <v>18.41544689632653</v>
       </c>
       <c r="P15">
-        <v>104.6442489991837</v>
+        <v>104.3541990791837</v>
       </c>
       <c r="Q15">
-        <v>139.4442489991837</v>
+        <v>139.1541990791837</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1091441263743504</v>
+        <v>0.1097826533173932</v>
       </c>
       <c r="T15">
-        <v>0.8719557425877323</v>
+        <v>0.8807453063034394</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>28.75231799864596</v>
+        <v>26.69858099874268</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1003987818529582</v>
+        <v>0.1002840237602315</v>
       </c>
       <c r="C16">
-        <v>595.4851710670529</v>
+        <v>588.8721538206672</v>
       </c>
       <c r="D16">
-        <v>414.6611710670528</v>
+        <v>414.8321538206672</v>
       </c>
       <c r="E16">
-        <v>-245.924</v>
+        <v>-239.14</v>
       </c>
       <c r="F16">
-        <v>94.976</v>
+        <v>101.76</v>
       </c>
       <c r="G16">
         <v>275.8</v>
@@ -2587,28 +2587,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M16">
-        <v>4.7772928</v>
+        <v>5.118528</v>
       </c>
       <c r="N16">
-        <v>122.7696459755102</v>
+        <v>122.4284107755102</v>
       </c>
       <c r="O16">
-        <v>18.41544689632653</v>
+        <v>18.36426161632653</v>
       </c>
       <c r="P16">
-        <v>104.3541990791837</v>
+        <v>104.0641491591837</v>
       </c>
       <c r="Q16">
-        <v>139.1541990791837</v>
+        <v>138.8641491591837</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1097826533173932</v>
+        <v>0.1104362044238017</v>
       </c>
       <c r="T16">
-        <v>0.8807453063034394</v>
+        <v>0.8897416832830455</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>26.69858099874268</v>
+        <v>24.9186755988265</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1002840237602315</v>
+        <v>0.1001692656675048</v>
       </c>
       <c r="C17">
-        <v>588.8721538206672</v>
+        <v>582.259277639633</v>
       </c>
       <c r="D17">
-        <v>414.8321538206672</v>
+        <v>415.0032776396329</v>
       </c>
       <c r="E17">
-        <v>-239.14</v>
+        <v>-232.356</v>
       </c>
       <c r="F17">
-        <v>101.76</v>
+        <v>108.544</v>
       </c>
       <c r="G17">
         <v>275.8</v>
@@ -2669,28 +2669,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M17">
-        <v>5.118528</v>
+        <v>5.459763199999999</v>
       </c>
       <c r="N17">
-        <v>122.4284107755102</v>
+        <v>122.0871755755102</v>
       </c>
       <c r="O17">
-        <v>18.36426161632653</v>
+        <v>18.31307633632653</v>
       </c>
       <c r="P17">
-        <v>104.0641491591837</v>
+        <v>103.7740992391837</v>
       </c>
       <c r="Q17">
-        <v>138.8641491591837</v>
+        <v>138.5740992391837</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1104362044238017</v>
+        <v>0.111105316270839</v>
       </c>
       <c r="T17">
-        <v>0.8897416832830455</v>
+        <v>0.8989522597145472</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.9186755988265</v>
+        <v>23.36125837389985</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1001692656675048</v>
+        <v>0.1000545075747781</v>
       </c>
       <c r="C18">
-        <v>582.259277639633</v>
+        <v>575.6465426985962</v>
       </c>
       <c r="D18">
-        <v>415.0032776396329</v>
+        <v>415.1745426985962</v>
       </c>
       <c r="E18">
-        <v>-232.356</v>
+        <v>-225.572</v>
       </c>
       <c r="F18">
-        <v>108.544</v>
+        <v>115.328</v>
       </c>
       <c r="G18">
         <v>275.8</v>
@@ -2751,28 +2751,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M18">
-        <v>5.459763199999999</v>
+        <v>5.8009984</v>
       </c>
       <c r="N18">
-        <v>122.0871755755102</v>
+        <v>121.7459403755102</v>
       </c>
       <c r="O18">
-        <v>18.31307633632653</v>
+        <v>18.26189105632653</v>
       </c>
       <c r="P18">
-        <v>103.7740992391837</v>
+        <v>103.4840493191837</v>
       </c>
       <c r="Q18">
-        <v>138.5740992391837</v>
+        <v>138.2840493191837</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.111105316270839</v>
+        <v>0.1117905512949133</v>
       </c>
       <c r="T18">
-        <v>0.8989522597145472</v>
+        <v>0.9083847777468077</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>23.36125837389985</v>
+        <v>21.98706670484691</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1000545075747781</v>
+        <v>0.09993974948205138</v>
       </c>
       <c r="C19">
-        <v>575.6465426985962</v>
+        <v>569.0339491724916</v>
       </c>
       <c r="D19">
-        <v>415.1745426985962</v>
+        <v>415.3459491724915</v>
       </c>
       <c r="E19">
-        <v>-225.572</v>
+        <v>-218.788</v>
       </c>
       <c r="F19">
-        <v>115.328</v>
+        <v>122.112</v>
       </c>
       <c r="G19">
         <v>275.8</v>
@@ -2833,28 +2833,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M19">
-        <v>5.8009984</v>
+        <v>6.1422336</v>
       </c>
       <c r="N19">
-        <v>121.7459403755102</v>
+        <v>121.4047051755102</v>
       </c>
       <c r="O19">
-        <v>18.26189105632653</v>
+        <v>18.21070577632653</v>
       </c>
       <c r="P19">
-        <v>103.4840493191837</v>
+        <v>103.1939993991837</v>
       </c>
       <c r="Q19">
-        <v>138.2840493191837</v>
+        <v>137.9939993991837</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1117905512949133</v>
+        <v>0.1124924993683553</v>
       </c>
       <c r="T19">
-        <v>0.9083847777468077</v>
+        <v>0.9180473571944892</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.98706670484691</v>
+        <v>20.76556299902208</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09993974948205139</v>
+        <v>0.0998249913893247</v>
       </c>
       <c r="C20">
-        <v>569.0339491724916</v>
+        <v>562.4214972365421</v>
       </c>
       <c r="D20">
-        <v>415.3459491724915</v>
+        <v>415.5174972365421</v>
       </c>
       <c r="E20">
-        <v>-218.788</v>
+        <v>-212.004</v>
       </c>
       <c r="F20">
-        <v>122.112</v>
+        <v>128.896</v>
       </c>
       <c r="G20">
         <v>275.8</v>
@@ -2915,28 +2915,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M20">
-        <v>6.142233599999999</v>
+        <v>6.483468799999999</v>
       </c>
       <c r="N20">
-        <v>121.4047051755102</v>
+        <v>121.0634699755102</v>
       </c>
       <c r="O20">
-        <v>18.21070577632653</v>
+        <v>18.15952049632653</v>
       </c>
       <c r="P20">
-        <v>103.1939993991837</v>
+        <v>102.9039494791837</v>
       </c>
       <c r="Q20">
-        <v>137.9939993991837</v>
+        <v>137.7039494791837</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1124924993683553</v>
+        <v>0.1132117794929934</v>
       </c>
       <c r="T20">
-        <v>0.9180473571944892</v>
+        <v>0.9279485188507555</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.76556299902209</v>
+        <v>19.6726386306525</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0998249913893247</v>
+        <v>0.09971023329659799</v>
       </c>
       <c r="C21">
-        <v>562.4214972365421</v>
+        <v>555.8091870662615</v>
       </c>
       <c r="D21">
-        <v>415.5174972365421</v>
+        <v>415.6891870662615</v>
       </c>
       <c r="E21">
-        <v>-212.004</v>
+        <v>-205.22</v>
       </c>
       <c r="F21">
-        <v>128.896</v>
+        <v>135.68</v>
       </c>
       <c r="G21">
         <v>275.8</v>
@@ -2997,28 +2997,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M21">
-        <v>6.483468799999999</v>
+        <v>6.824704</v>
       </c>
       <c r="N21">
-        <v>121.0634699755102</v>
+        <v>120.7222347755102</v>
       </c>
       <c r="O21">
-        <v>18.15952049632653</v>
+        <v>18.10833521632653</v>
       </c>
       <c r="P21">
-        <v>102.9039494791837</v>
+        <v>102.6138995591837</v>
       </c>
       <c r="Q21">
-        <v>137.7039494791837</v>
+        <v>137.4138995591837</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1132117794929934</v>
+        <v>0.1139490416207475</v>
       </c>
       <c r="T21">
-        <v>0.9279485188507555</v>
+        <v>0.9380972095484285</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.6726386306525</v>
+        <v>18.68900669911988</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09971023329659799</v>
+        <v>0.09959547520387128</v>
       </c>
       <c r="C22">
-        <v>555.8091870662615</v>
+        <v>549.1970188374528</v>
       </c>
       <c r="D22">
-        <v>415.6891870662615</v>
+        <v>415.8610188374528</v>
       </c>
       <c r="E22">
-        <v>-205.22</v>
+        <v>-198.436</v>
       </c>
       <c r="F22">
-        <v>135.68</v>
+        <v>142.464</v>
       </c>
       <c r="G22">
         <v>275.8</v>
@@ -3079,28 +3079,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M22">
-        <v>6.824704</v>
+        <v>7.1659392</v>
       </c>
       <c r="N22">
-        <v>120.7222347755102</v>
+        <v>120.3809995755102</v>
       </c>
       <c r="O22">
-        <v>18.10833521632653</v>
+        <v>18.05714993632653</v>
       </c>
       <c r="P22">
-        <v>102.6138995591837</v>
+        <v>102.3238496391837</v>
       </c>
       <c r="Q22">
-        <v>137.4138995591837</v>
+        <v>137.1238496391837</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1139490416207475</v>
+        <v>0.1147049686124953</v>
       </c>
       <c r="T22">
-        <v>0.9380972095484285</v>
+        <v>0.9485028291245237</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.68900669911988</v>
+        <v>17.79905399916179</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09959547520387128</v>
+        <v>0.09948071711114459</v>
       </c>
       <c r="C23">
-        <v>549.1970188374528</v>
+        <v>542.5849927262102</v>
       </c>
       <c r="D23">
-        <v>415.8610188374528</v>
+        <v>416.0329927262101</v>
       </c>
       <c r="E23">
-        <v>-198.436</v>
+        <v>-191.652</v>
       </c>
       <c r="F23">
-        <v>142.464</v>
+        <v>149.248</v>
       </c>
       <c r="G23">
         <v>275.8</v>
@@ -3161,28 +3161,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M23">
-        <v>7.1659392</v>
+        <v>7.507174399999999</v>
       </c>
       <c r="N23">
-        <v>120.3809995755102</v>
+        <v>120.0397643755102</v>
       </c>
       <c r="O23">
-        <v>18.05714993632653</v>
+        <v>18.00596465632653</v>
       </c>
       <c r="P23">
-        <v>102.3238496391837</v>
+        <v>102.0337997191837</v>
       </c>
       <c r="Q23">
-        <v>137.1238496391837</v>
+        <v>136.8337997191837</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1147049686124953</v>
+        <v>0.1154802783476213</v>
       </c>
       <c r="T23">
-        <v>0.9485028291245234</v>
+        <v>0.9591752594589801</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.79905399916179</v>
+        <v>16.99000609010898</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09948071711114459</v>
+        <v>0.09936595901841788</v>
       </c>
       <c r="C24">
-        <v>542.5849927262102</v>
+        <v>535.973108908919</v>
       </c>
       <c r="D24">
-        <v>416.0329927262101</v>
+        <v>416.205108908919</v>
       </c>
       <c r="E24">
-        <v>-191.652</v>
+        <v>-184.868</v>
       </c>
       <c r="F24">
-        <v>149.248</v>
+        <v>156.032</v>
       </c>
       <c r="G24">
         <v>275.8</v>
@@ -3243,28 +3243,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M24">
-        <v>7.507174399999999</v>
+        <v>7.8484096</v>
       </c>
       <c r="N24">
-        <v>120.0397643755102</v>
+        <v>119.6985291755102</v>
       </c>
       <c r="O24">
-        <v>18.00596465632653</v>
+        <v>17.95477937632653</v>
       </c>
       <c r="P24">
-        <v>102.0337997191837</v>
+        <v>101.7437497991837</v>
       </c>
       <c r="Q24">
-        <v>136.8337997191837</v>
+        <v>136.5437497991837</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1154802783476213</v>
+        <v>0.1162757259979453</v>
       </c>
       <c r="T24">
-        <v>0.9591752594589801</v>
+        <v>0.9701248957761496</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.99000609010898</v>
+        <v>16.25131017314772</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09936595901841788</v>
+        <v>0.09925120092569117</v>
       </c>
       <c r="C25">
-        <v>535.973108908919</v>
+        <v>529.3613675622569</v>
       </c>
       <c r="D25">
-        <v>416.205108908919</v>
+        <v>416.3773675622569</v>
       </c>
       <c r="E25">
-        <v>-184.868</v>
+        <v>-178.084</v>
       </c>
       <c r="F25">
-        <v>156.032</v>
+        <v>162.816</v>
       </c>
       <c r="G25">
         <v>275.8</v>
@@ -3325,28 +3325,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M25">
-        <v>7.8484096</v>
+        <v>8.1896448</v>
       </c>
       <c r="N25">
-        <v>119.6985291755102</v>
+        <v>119.3572939755102</v>
       </c>
       <c r="O25">
-        <v>17.95477937632653</v>
+        <v>17.90359409632653</v>
       </c>
       <c r="P25">
-        <v>101.7437497991837</v>
+        <v>101.4536998791837</v>
       </c>
       <c r="Q25">
-        <v>136.5437497991837</v>
+        <v>136.2536998791837</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1162757259979453</v>
+        <v>0.1170921064811726</v>
       </c>
       <c r="T25">
-        <v>0.9701248957761496</v>
+        <v>0.9813626804174553</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.25131017314772</v>
+        <v>15.57417224926656</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09925120092569117</v>
+        <v>0.09913644283296447</v>
       </c>
       <c r="C26">
-        <v>529.3613675622569</v>
+        <v>522.7497688631942</v>
       </c>
       <c r="D26">
-        <v>416.3773675622569</v>
+        <v>416.5497688631942</v>
       </c>
       <c r="E26">
-        <v>-178.084</v>
+        <v>-171.3</v>
       </c>
       <c r="F26">
-        <v>162.816</v>
+        <v>169.6</v>
       </c>
       <c r="G26">
         <v>275.8</v>
@@ -3407,28 +3407,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M26">
-        <v>8.1896448</v>
+        <v>8.53088</v>
       </c>
       <c r="N26">
-        <v>119.3572939755102</v>
+        <v>119.0160587755102</v>
       </c>
       <c r="O26">
-        <v>17.90359409632653</v>
+        <v>17.85240881632653</v>
       </c>
       <c r="P26">
-        <v>101.4536998791837</v>
+        <v>101.1636499591837</v>
       </c>
       <c r="Q26">
-        <v>136.2536998791837</v>
+        <v>135.9636499591837</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1170921064811726</v>
+        <v>0.1179302571106193</v>
       </c>
       <c r="T26">
-        <v>0.9813626804174553</v>
+        <v>0.9929001393158624</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.57417224926656</v>
+        <v>14.9512053592959</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09913644283296447</v>
+        <v>0.09902168474023779</v>
       </c>
       <c r="C27">
-        <v>522.7497688631942</v>
+        <v>516.1383129889941</v>
       </c>
       <c r="D27">
-        <v>416.5497688631942</v>
+        <v>416.7223129889941</v>
       </c>
       <c r="E27">
-        <v>-171.3</v>
+        <v>-164.516</v>
       </c>
       <c r="F27">
-        <v>169.6</v>
+        <v>176.384</v>
       </c>
       <c r="G27">
         <v>275.8</v>
@@ -3489,28 +3489,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M27">
-        <v>8.53088</v>
+        <v>8.8721152</v>
       </c>
       <c r="N27">
-        <v>119.0160587755102</v>
+        <v>118.6748235755102</v>
       </c>
       <c r="O27">
-        <v>17.85240881632653</v>
+        <v>17.80122353632653</v>
       </c>
       <c r="P27">
-        <v>101.1636499591837</v>
+        <v>100.8736000391837</v>
       </c>
       <c r="Q27">
-        <v>135.9636499591837</v>
+        <v>135.6736000391837</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1179302571106193</v>
+        <v>0.1187910604597808</v>
       </c>
       <c r="T27">
-        <v>0.9929001393158624</v>
+        <v>1.00474942142774</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.9512053592959</v>
+        <v>14.37615899932298</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09902168474023779</v>
+        <v>0.09890692664751108</v>
       </c>
       <c r="C28">
-        <v>516.1383129889941</v>
+        <v>509.5270001172137</v>
       </c>
       <c r="D28">
-        <v>416.7223129889941</v>
+        <v>416.8950001172137</v>
       </c>
       <c r="E28">
-        <v>-164.516</v>
+        <v>-157.732</v>
       </c>
       <c r="F28">
-        <v>176.384</v>
+        <v>183.168</v>
       </c>
       <c r="G28">
         <v>275.8</v>
@@ -3571,28 +3571,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M28">
-        <v>8.8721152</v>
+        <v>9.213350399999999</v>
       </c>
       <c r="N28">
-        <v>118.6748235755102</v>
+        <v>118.3335883755102</v>
       </c>
       <c r="O28">
-        <v>17.80122353632653</v>
+        <v>17.75003825632653</v>
       </c>
       <c r="P28">
-        <v>100.8736000391837</v>
+        <v>100.5835501191837</v>
       </c>
       <c r="Q28">
-        <v>135.6736000391837</v>
+        <v>135.3835501191837</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1187910604597808</v>
+        <v>0.119675447462344</v>
       </c>
       <c r="T28">
-        <v>1.00474942142774</v>
+        <v>1.016923341405697</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.37615899932298</v>
+        <v>13.84370866601472</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09890692664751108</v>
+        <v>0.0987921685547844</v>
       </c>
       <c r="C29">
-        <v>509.5270001172137</v>
+        <v>502.9158304257048</v>
       </c>
       <c r="D29">
-        <v>416.8950001172137</v>
+        <v>417.0678304257048</v>
       </c>
       <c r="E29">
-        <v>-157.732</v>
+        <v>-150.948</v>
       </c>
       <c r="F29">
-        <v>183.168</v>
+        <v>189.952</v>
       </c>
       <c r="G29">
         <v>275.8</v>
@@ -3653,28 +3653,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M29">
-        <v>9.213350399999999</v>
+        <v>9.554585599999999</v>
       </c>
       <c r="N29">
-        <v>118.3335883755102</v>
+        <v>117.9923531755102</v>
       </c>
       <c r="O29">
-        <v>17.75003825632653</v>
+        <v>17.69885297632653</v>
       </c>
       <c r="P29">
-        <v>100.5835501191837</v>
+        <v>100.2935001991837</v>
       </c>
       <c r="Q29">
-        <v>135.3835501191837</v>
+        <v>135.0935001991837</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.119675447462344</v>
+        <v>0.1205844007705339</v>
       </c>
       <c r="T29">
-        <v>1.016923341405697</v>
+        <v>1.029435425827485</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.84370866601472</v>
+        <v>13.34929049937134</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0987921685547844</v>
+        <v>0.0986774104620577</v>
       </c>
       <c r="C30">
-        <v>502.9158304257048</v>
+        <v>496.3048040926141</v>
       </c>
       <c r="D30">
-        <v>417.0678304257048</v>
+        <v>417.2408040926141</v>
       </c>
       <c r="E30">
-        <v>-150.948</v>
+        <v>-144.164</v>
       </c>
       <c r="F30">
-        <v>189.952</v>
+        <v>196.736</v>
       </c>
       <c r="G30">
         <v>275.8</v>
@@ -3735,28 +3735,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M30">
-        <v>9.554585599999999</v>
+        <v>9.895820800000001</v>
       </c>
       <c r="N30">
-        <v>117.9923531755102</v>
+        <v>117.6511179755102</v>
       </c>
       <c r="O30">
-        <v>17.69885297632653</v>
+        <v>17.64766769632653</v>
       </c>
       <c r="P30">
-        <v>100.2935001991837</v>
+        <v>100.0034502791837</v>
       </c>
       <c r="Q30">
-        <v>135.0935001991837</v>
+        <v>134.8034502791837</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1205844007705339</v>
+        <v>0.1215189583972644</v>
       </c>
       <c r="T30">
-        <v>1.029435425827485</v>
+        <v>1.042299963331578</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.34929049937134</v>
+        <v>12.88897013732405</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09867741046205769</v>
+        <v>0.09894515236933099</v>
       </c>
       <c r="C31">
-        <v>496.3048040926141</v>
+        <v>489.1174624395364</v>
       </c>
       <c r="D31">
-        <v>417.2408040926141</v>
+        <v>416.8374624395364</v>
       </c>
       <c r="E31">
-        <v>-144.164</v>
+        <v>-137.38</v>
       </c>
       <c r="F31">
-        <v>196.736</v>
+        <v>203.52</v>
       </c>
       <c r="G31">
         <v>275.8</v>
@@ -3817,45 +3817,45 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M31">
-        <v>9.895820799999999</v>
+        <v>10.542336</v>
       </c>
       <c r="N31">
-        <v>117.6511179755102</v>
+        <v>117.0046027755102</v>
       </c>
       <c r="O31">
-        <v>17.64766769632653</v>
+        <v>17.55069041632653</v>
       </c>
       <c r="P31">
-        <v>100.0034502791837</v>
+        <v>99.45391235918369</v>
       </c>
       <c r="Q31">
-        <v>134.8034502791837</v>
+        <v>134.2539123591837</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1215189583972644</v>
+        <v>0.1224802176704728</v>
       </c>
       <c r="T31">
-        <v>1.042299963331578</v>
+        <v>1.055532059050073</v>
       </c>
       <c r="U31">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y31">
-        <v>12.88897013732405</v>
+        <v>12.09854616429511</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09894515236933099</v>
+        <v>0.0988431442766043</v>
       </c>
       <c r="C32">
-        <v>489.1174624395364</v>
+        <v>482.4870412500196</v>
       </c>
       <c r="D32">
-        <v>416.8374624395364</v>
+        <v>416.9910412500196</v>
       </c>
       <c r="E32">
-        <v>-137.38</v>
+        <v>-130.596</v>
       </c>
       <c r="F32">
-        <v>203.52</v>
+        <v>210.304</v>
       </c>
       <c r="G32">
         <v>275.8</v>
@@ -3899,28 +3899,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M32">
-        <v>10.542336</v>
+        <v>10.8937472</v>
       </c>
       <c r="N32">
-        <v>117.0046027755102</v>
+        <v>116.6531915755102</v>
       </c>
       <c r="O32">
-        <v>17.55069041632653</v>
+        <v>17.49797873632653</v>
       </c>
       <c r="P32">
-        <v>99.45391235918369</v>
+        <v>99.15521283918369</v>
       </c>
       <c r="Q32">
-        <v>134.2539123591837</v>
+        <v>133.9552128391837</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1224802176704728</v>
+        <v>0.1234693395313106</v>
       </c>
       <c r="T32">
-        <v>1.055532059050073</v>
+        <v>1.069147693774901</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>12.09854616429511</v>
+        <v>11.70827048157591</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0988431442766043</v>
+        <v>0.09874113618387761</v>
       </c>
       <c r="C33">
-        <v>482.4870412500196</v>
+        <v>475.8567332707898</v>
       </c>
       <c r="D33">
-        <v>416.9910412500196</v>
+        <v>417.1447332707898</v>
       </c>
       <c r="E33">
-        <v>-130.596</v>
+        <v>-123.812</v>
       </c>
       <c r="F33">
-        <v>210.304</v>
+        <v>217.088</v>
       </c>
       <c r="G33">
         <v>275.8</v>
@@ -3981,28 +3981,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M33">
-        <v>10.8937472</v>
+        <v>11.2451584</v>
       </c>
       <c r="N33">
-        <v>116.6531915755102</v>
+        <v>116.3017803755102</v>
       </c>
       <c r="O33">
-        <v>17.49797873632653</v>
+        <v>17.44526705632653</v>
       </c>
       <c r="P33">
-        <v>99.15521283918369</v>
+        <v>98.85651331918369</v>
       </c>
       <c r="Q33">
-        <v>133.9552128391837</v>
+        <v>133.6565133191837</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1234693395313106</v>
+        <v>0.1244875532115847</v>
       </c>
       <c r="T33">
-        <v>1.069147693774901</v>
+        <v>1.083163788344577</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.70827048157591</v>
+        <v>11.34238702902666</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09874113618387761</v>
+        <v>0.09863912809115088</v>
       </c>
       <c r="C34">
-        <v>475.8567332707898</v>
+        <v>469.2265386270723</v>
       </c>
       <c r="D34">
-        <v>417.1447332707898</v>
+        <v>417.2985386270723</v>
       </c>
       <c r="E34">
-        <v>-123.812</v>
+        <v>-117.028</v>
       </c>
       <c r="F34">
-        <v>217.088</v>
+        <v>223.872</v>
       </c>
       <c r="G34">
         <v>275.8</v>
@@ -4063,28 +4063,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M34">
-        <v>11.2451584</v>
+        <v>11.5965696</v>
       </c>
       <c r="N34">
-        <v>116.3017803755102</v>
+        <v>115.9503691755102</v>
       </c>
       <c r="O34">
-        <v>17.44526705632653</v>
+        <v>17.39255537632653</v>
       </c>
       <c r="P34">
-        <v>98.85651331918369</v>
+        <v>98.55781379918369</v>
       </c>
       <c r="Q34">
-        <v>133.6565133191837</v>
+        <v>133.3578137991837</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1244875532115847</v>
+        <v>0.125536161330076</v>
       </c>
       <c r="T34">
-        <v>1.083163788344577</v>
+        <v>1.09759827379693</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.34238702902666</v>
+        <v>10.99867833117737</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09863912809115088</v>
+        <v>0.0985371199984242</v>
       </c>
       <c r="C35">
-        <v>469.2265386270723</v>
+        <v>462.5964574442771</v>
       </c>
       <c r="D35">
-        <v>417.2985386270723</v>
+        <v>417.4524574442771</v>
       </c>
       <c r="E35">
-        <v>-117.028</v>
+        <v>-110.244</v>
       </c>
       <c r="F35">
-        <v>223.872</v>
+        <v>230.656</v>
       </c>
       <c r="G35">
         <v>275.8</v>
@@ -4145,28 +4145,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M35">
-        <v>11.5965696</v>
+        <v>11.9479808</v>
       </c>
       <c r="N35">
-        <v>115.9503691755102</v>
+        <v>115.5989579755102</v>
       </c>
       <c r="O35">
-        <v>17.39255537632653</v>
+        <v>17.33984369632653</v>
       </c>
       <c r="P35">
-        <v>98.55781379918369</v>
+        <v>98.25911427918368</v>
       </c>
       <c r="Q35">
-        <v>133.3578137991837</v>
+        <v>133.0591142791837</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.125536161330076</v>
+        <v>0.1266165454521579</v>
       </c>
       <c r="T35">
-        <v>1.09759827379693</v>
+        <v>1.112470167899355</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.99867833117737</v>
+        <v>10.67518779202509</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0985371199984242</v>
+        <v>0.09843511190569751</v>
       </c>
       <c r="C36">
-        <v>462.5964574442771</v>
+        <v>455.9664898479989</v>
       </c>
       <c r="D36">
-        <v>417.4524574442771</v>
+        <v>417.606489847999</v>
       </c>
       <c r="E36">
-        <v>-110.244</v>
+        <v>-103.46</v>
       </c>
       <c r="F36">
-        <v>230.656</v>
+        <v>237.44</v>
       </c>
       <c r="G36">
         <v>275.8</v>
@@ -4227,28 +4227,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M36">
-        <v>11.9479808</v>
+        <v>12.299392</v>
       </c>
       <c r="N36">
-        <v>115.5989579755102</v>
+        <v>115.2475467755102</v>
       </c>
       <c r="O36">
-        <v>17.33984369632653</v>
+        <v>17.28713201632653</v>
       </c>
       <c r="P36">
-        <v>98.25911427918368</v>
+        <v>97.96041475918369</v>
       </c>
       <c r="Q36">
-        <v>133.0591142791837</v>
+        <v>132.7604147591837</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1266165454521579</v>
+        <v>0.1277301721626116</v>
       </c>
       <c r="T36">
-        <v>1.112470167899355</v>
+        <v>1.127799658743392</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.67518779202509</v>
+        <v>10.37018242653866</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09843511190569751</v>
+        <v>0.09833310381297081</v>
       </c>
       <c r="C37">
-        <v>455.9664898479989</v>
+        <v>449.3366359640188</v>
       </c>
       <c r="D37">
-        <v>417.606489847999</v>
+        <v>417.7606359640188</v>
       </c>
       <c r="E37">
-        <v>-103.46</v>
+        <v>-96.67599999999996</v>
       </c>
       <c r="F37">
-        <v>237.44</v>
+        <v>244.224</v>
       </c>
       <c r="G37">
         <v>275.8</v>
@@ -4309,28 +4309,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M37">
-        <v>12.299392</v>
+        <v>12.6508032</v>
       </c>
       <c r="N37">
-        <v>115.2475467755102</v>
+        <v>114.8961355755102</v>
       </c>
       <c r="O37">
-        <v>17.28713201632653</v>
+        <v>17.23442033632653</v>
       </c>
       <c r="P37">
-        <v>97.96041475918369</v>
+        <v>97.66171523918368</v>
       </c>
       <c r="Q37">
-        <v>132.7604147591837</v>
+        <v>132.4617152391837</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1277301721626116</v>
+        <v>0.1288785997077669</v>
       </c>
       <c r="T37">
-        <v>1.127799658743392</v>
+        <v>1.143608196176306</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.37018242653866</v>
+        <v>10.08212180357926</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09833310381297081</v>
+        <v>0.09876574572024412</v>
       </c>
       <c r="C38">
-        <v>449.3366359640189</v>
+        <v>441.8996445760018</v>
       </c>
       <c r="D38">
-        <v>417.7606359640188</v>
+        <v>417.1076445760017</v>
       </c>
       <c r="E38">
-        <v>-96.67599999999999</v>
+        <v>-89.892</v>
       </c>
       <c r="F38">
-        <v>244.224</v>
+        <v>251.008</v>
       </c>
       <c r="G38">
         <v>275.8</v>
@@ -4391,45 +4391,45 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M38">
-        <v>12.6508032</v>
+        <v>13.428928</v>
       </c>
       <c r="N38">
-        <v>114.8961355755102</v>
+        <v>114.1180107755102</v>
       </c>
       <c r="O38">
-        <v>17.23442033632653</v>
+        <v>17.11770161632653</v>
       </c>
       <c r="P38">
-        <v>97.66171523918368</v>
+        <v>97.00030915918369</v>
       </c>
       <c r="Q38">
-        <v>132.4617152391837</v>
+        <v>131.8003091591837</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1288785997077669</v>
+        <v>0.1300634852702288</v>
       </c>
       <c r="T38">
-        <v>1.143608196176306</v>
+        <v>1.159918591940423</v>
       </c>
       <c r="U38">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>10.08212180357926</v>
+        <v>9.497924091596159</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09876574572024412</v>
+        <v>0.09867818762751743</v>
       </c>
       <c r="C39">
-        <v>441.8996445760018</v>
+        <v>435.2476321967483</v>
       </c>
       <c r="D39">
-        <v>417.1076445760017</v>
+        <v>417.2396321967482</v>
       </c>
       <c r="E39">
-        <v>-89.892</v>
+        <v>-83.108</v>
       </c>
       <c r="F39">
-        <v>251.008</v>
+        <v>257.792</v>
       </c>
       <c r="G39">
         <v>275.8</v>
@@ -4473,28 +4473,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M39">
-        <v>13.428928</v>
+        <v>13.791872</v>
       </c>
       <c r="N39">
-        <v>114.1180107755102</v>
+        <v>113.7550667755102</v>
       </c>
       <c r="O39">
-        <v>17.11770161632653</v>
+        <v>17.06326001632653</v>
       </c>
       <c r="P39">
-        <v>97.00030915918369</v>
+        <v>96.69180675918369</v>
       </c>
       <c r="Q39">
-        <v>131.8003091591837</v>
+        <v>131.4918067591837</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1300634852702288</v>
+        <v>0.1312865929476087</v>
       </c>
       <c r="T39">
-        <v>1.159918591940423</v>
+        <v>1.176755129503383</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.497924091596159</v>
+        <v>9.247978720764682</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09867818762751743</v>
+        <v>0.09859062953479071</v>
       </c>
       <c r="C40">
-        <v>435.2476321967483</v>
+        <v>428.595703375044</v>
       </c>
       <c r="D40">
-        <v>417.2396321967482</v>
+        <v>417.371703375044</v>
       </c>
       <c r="E40">
-        <v>-83.108</v>
+        <v>-76.32399999999996</v>
       </c>
       <c r="F40">
-        <v>257.792</v>
+        <v>264.576</v>
       </c>
       <c r="G40">
         <v>275.8</v>
@@ -4555,28 +4555,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M40">
-        <v>13.791872</v>
+        <v>14.154816</v>
       </c>
       <c r="N40">
-        <v>113.7550667755102</v>
+        <v>113.3921227755102</v>
       </c>
       <c r="O40">
-        <v>17.06326001632653</v>
+        <v>17.00881841632653</v>
       </c>
       <c r="P40">
-        <v>96.69180675918369</v>
+        <v>96.38330435918368</v>
       </c>
       <c r="Q40">
-        <v>131.4918067591837</v>
+        <v>131.1833043591837</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1312865929476087</v>
+        <v>0.1325498025160504</v>
       </c>
       <c r="T40">
-        <v>1.176755129503383</v>
+        <v>1.194143684691358</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.247978720764682</v>
+        <v>9.010851061257894</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09859062953479071</v>
+        <v>0.09850307144206402</v>
       </c>
       <c r="C41">
-        <v>428.595703375044</v>
+        <v>421.9438581902613</v>
       </c>
       <c r="D41">
-        <v>417.371703375044</v>
+        <v>417.5038581902612</v>
       </c>
       <c r="E41">
-        <v>-76.32399999999996</v>
+        <v>-69.53999999999996</v>
       </c>
       <c r="F41">
-        <v>264.576</v>
+        <v>271.36</v>
       </c>
       <c r="G41">
         <v>275.8</v>
@@ -4637,28 +4637,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M41">
-        <v>14.154816</v>
+        <v>14.51776</v>
       </c>
       <c r="N41">
-        <v>113.3921227755102</v>
+        <v>113.0291787755102</v>
       </c>
       <c r="O41">
-        <v>17.00881841632653</v>
+        <v>16.95437681632653</v>
       </c>
       <c r="P41">
-        <v>96.38330435918368</v>
+        <v>96.07480195918369</v>
       </c>
       <c r="Q41">
-        <v>131.1833043591837</v>
+        <v>130.8748019591837</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1325498025160504</v>
+        <v>0.1338551190701067</v>
       </c>
       <c r="T41">
-        <v>1.194143684691358</v>
+        <v>1.212111858385599</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.010851061257894</v>
+        <v>8.785579784726446</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09850307144206402</v>
+        <v>0.09841551334933733</v>
       </c>
       <c r="C42">
-        <v>421.9438581902613</v>
+        <v>415.2920967218722</v>
       </c>
       <c r="D42">
-        <v>417.5038581902612</v>
+        <v>417.6360967218722</v>
       </c>
       <c r="E42">
-        <v>-69.53999999999996</v>
+        <v>-62.75599999999997</v>
       </c>
       <c r="F42">
-        <v>271.36</v>
+        <v>278.144</v>
       </c>
       <c r="G42">
         <v>275.8</v>
@@ -4719,28 +4719,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M42">
-        <v>14.51776</v>
+        <v>14.880704</v>
       </c>
       <c r="N42">
-        <v>113.0291787755102</v>
+        <v>112.6662347755102</v>
       </c>
       <c r="O42">
-        <v>16.95437681632653</v>
+        <v>16.89993521632653</v>
       </c>
       <c r="P42">
-        <v>96.07480195918369</v>
+        <v>95.76629955918369</v>
       </c>
       <c r="Q42">
-        <v>130.8748019591837</v>
+        <v>130.5662995591837</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1338551190701067</v>
+        <v>0.1352046836429446</v>
       </c>
       <c r="T42">
-        <v>1.212111858385599</v>
+        <v>1.230689122713542</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.785579784726446</v>
+        <v>8.57129735095263</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09841551334933733</v>
+        <v>0.09832795525661062</v>
       </c>
       <c r="C43">
-        <v>415.2920967218722</v>
+        <v>408.6404190494503</v>
       </c>
       <c r="D43">
-        <v>417.6360967218722</v>
+        <v>417.7684190494503</v>
       </c>
       <c r="E43">
-        <v>-62.75599999999997</v>
+        <v>-55.97199999999998</v>
       </c>
       <c r="F43">
-        <v>278.144</v>
+        <v>284.928</v>
       </c>
       <c r="G43">
         <v>275.8</v>
@@ -4801,28 +4801,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M43">
-        <v>14.880704</v>
+        <v>15.243648</v>
       </c>
       <c r="N43">
-        <v>112.6662347755102</v>
+        <v>112.3032907755102</v>
       </c>
       <c r="O43">
-        <v>16.89993521632653</v>
+        <v>16.84549361632653</v>
       </c>
       <c r="P43">
-        <v>95.76629955918369</v>
+        <v>95.45779715918368</v>
       </c>
       <c r="Q43">
-        <v>130.5662995591837</v>
+        <v>130.2577971591837</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1352046836429446</v>
+        <v>0.1366007849251907</v>
       </c>
       <c r="T43">
-        <v>1.230689122713542</v>
+        <v>1.249906982363139</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.57129735095263</v>
+        <v>8.367218842596616</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09832795525661062</v>
+        <v>0.09824039716388393</v>
       </c>
       <c r="C44">
-        <v>408.6404190494503</v>
+        <v>401.9888252526695</v>
       </c>
       <c r="D44">
-        <v>417.7684190494503</v>
+        <v>417.9008252526694</v>
       </c>
       <c r="E44">
-        <v>-55.97199999999998</v>
+        <v>-49.18799999999999</v>
       </c>
       <c r="F44">
-        <v>284.928</v>
+        <v>291.712</v>
       </c>
       <c r="G44">
         <v>275.8</v>
@@ -4883,28 +4883,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M44">
-        <v>15.243648</v>
+        <v>15.606592</v>
       </c>
       <c r="N44">
-        <v>112.3032907755102</v>
+        <v>111.9403467755102</v>
       </c>
       <c r="O44">
-        <v>16.84549361632653</v>
+        <v>16.79105201632653</v>
       </c>
       <c r="P44">
-        <v>95.45779715918368</v>
+        <v>95.14929475918369</v>
       </c>
       <c r="Q44">
-        <v>130.2577971591837</v>
+        <v>129.9492947591837</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1366007849251907</v>
+        <v>0.1380458722173402</v>
       </c>
       <c r="T44">
-        <v>1.249906982363139</v>
+        <v>1.269799152877634</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.367218842596616</v>
+        <v>8.172632357885067</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09824039716388393</v>
+        <v>0.09815283907115724</v>
       </c>
       <c r="C45">
-        <v>401.9888252526695</v>
+        <v>395.337315411305</v>
       </c>
       <c r="D45">
-        <v>417.9008252526694</v>
+        <v>418.033315411305</v>
       </c>
       <c r="E45">
-        <v>-49.18799999999999</v>
+        <v>-42.404</v>
       </c>
       <c r="F45">
-        <v>291.712</v>
+        <v>298.496</v>
       </c>
       <c r="G45">
         <v>275.8</v>
@@ -4965,28 +4965,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M45">
-        <v>15.606592</v>
+        <v>15.969536</v>
       </c>
       <c r="N45">
-        <v>111.9403467755102</v>
+        <v>111.5774027755102</v>
       </c>
       <c r="O45">
-        <v>16.79105201632653</v>
+        <v>16.73661041632653</v>
       </c>
       <c r="P45">
-        <v>95.14929475918369</v>
+        <v>94.84079235918369</v>
       </c>
       <c r="Q45">
-        <v>129.9492947591837</v>
+        <v>129.6407923591837</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1380458722173402</v>
+        <v>0.1395425697699236</v>
       </c>
       <c r="T45">
-        <v>1.269799152877634</v>
+        <v>1.290401758053361</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.172632357885067</v>
+        <v>7.98689071338768</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09815283907115724</v>
+        <v>0.09806528097843055</v>
       </c>
       <c r="C46">
-        <v>395.337315411305</v>
+        <v>388.685889605233</v>
       </c>
       <c r="D46">
-        <v>418.033315411305</v>
+        <v>418.165889605233</v>
       </c>
       <c r="E46">
-        <v>-42.404</v>
+        <v>-35.62</v>
       </c>
       <c r="F46">
-        <v>298.496</v>
+        <v>305.28</v>
       </c>
       <c r="G46">
         <v>275.8</v>
@@ -5047,28 +5047,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M46">
-        <v>15.969536</v>
+        <v>16.33248</v>
       </c>
       <c r="N46">
-        <v>111.5774027755102</v>
+        <v>111.2144587755102</v>
       </c>
       <c r="O46">
-        <v>16.73661041632653</v>
+        <v>16.68216881632653</v>
       </c>
       <c r="P46">
-        <v>94.84079235918369</v>
+        <v>94.53228995918369</v>
       </c>
       <c r="Q46">
-        <v>129.6407923591837</v>
+        <v>129.3322899591837</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1395425697699236</v>
+        <v>0.1410936926880555</v>
       </c>
       <c r="T46">
-        <v>1.290401758053361</v>
+        <v>1.311753548871842</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.98689071338768</v>
+        <v>7.809404253090176</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09806528097843055</v>
+        <v>0.09797772288570383</v>
       </c>
       <c r="C47">
-        <v>388.685889605233</v>
+        <v>382.0345479144312</v>
       </c>
       <c r="D47">
-        <v>418.165889605233</v>
+        <v>418.2985479144313</v>
       </c>
       <c r="E47">
-        <v>-35.62</v>
+        <v>-28.83599999999996</v>
       </c>
       <c r="F47">
-        <v>305.28</v>
+        <v>312.064</v>
       </c>
       <c r="G47">
         <v>275.8</v>
@@ -5129,28 +5129,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M47">
-        <v>16.33248</v>
+        <v>16.695424</v>
       </c>
       <c r="N47">
-        <v>111.2144587755102</v>
+        <v>110.8515147755102</v>
       </c>
       <c r="O47">
-        <v>16.68216881632653</v>
+        <v>16.62772721632653</v>
       </c>
       <c r="P47">
-        <v>94.53228995918369</v>
+        <v>94.22378755918368</v>
       </c>
       <c r="Q47">
-        <v>129.3322899591837</v>
+        <v>129.0237875591837</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1410936926880555</v>
+        <v>0.1427022646031552</v>
       </c>
       <c r="T47">
-        <v>1.311753548871842</v>
+        <v>1.333896146757674</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.809404253090176</v>
+        <v>7.639634595414301</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09797772288570383</v>
+        <v>0.09820976479297715</v>
       </c>
       <c r="C48">
-        <v>382.0345479144312</v>
+        <v>374.8991676430362</v>
       </c>
       <c r="D48">
-        <v>418.2985479144313</v>
+        <v>417.9471676430362</v>
       </c>
       <c r="E48">
-        <v>-28.83599999999996</v>
+        <v>-22.05199999999996</v>
       </c>
       <c r="F48">
-        <v>312.064</v>
+        <v>318.848</v>
       </c>
       <c r="G48">
         <v>275.8</v>
@@ -5211,45 +5211,45 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M48">
-        <v>16.695424</v>
+        <v>17.3134464</v>
       </c>
       <c r="N48">
-        <v>110.8515147755102</v>
+        <v>110.2334923755102</v>
       </c>
       <c r="O48">
-        <v>16.62772721632653</v>
+        <v>16.53502385632653</v>
       </c>
       <c r="P48">
-        <v>94.22378755918368</v>
+        <v>93.69846851918368</v>
       </c>
       <c r="Q48">
-        <v>129.0237875591837</v>
+        <v>128.4984685191837</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1427022646031552</v>
+        <v>0.1443715373452399</v>
       </c>
       <c r="T48">
-        <v>1.333896146757674</v>
+        <v>1.356874314375047</v>
       </c>
       <c r="U48">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y48">
-        <v>7.639634595414301</v>
+        <v>7.366929485253162</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09820976479297715</v>
+        <v>0.09812900670025043</v>
       </c>
       <c r="C49">
-        <v>374.8991676430362</v>
+        <v>368.2373923535359</v>
       </c>
       <c r="D49">
-        <v>417.9471676430362</v>
+        <v>418.0693923535359</v>
       </c>
       <c r="E49">
-        <v>-22.05199999999996</v>
+        <v>-15.26799999999997</v>
       </c>
       <c r="F49">
-        <v>318.848</v>
+        <v>325.632</v>
       </c>
       <c r="G49">
         <v>275.8</v>
@@ -5293,28 +5293,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M49">
-        <v>17.3134464</v>
+        <v>17.6818176</v>
       </c>
       <c r="N49">
-        <v>110.2334923755102</v>
+        <v>109.8651211755102</v>
       </c>
       <c r="O49">
-        <v>16.53502385632653</v>
+        <v>16.47976817632653</v>
       </c>
       <c r="P49">
-        <v>93.69846851918368</v>
+        <v>93.38535299918368</v>
       </c>
       <c r="Q49">
-        <v>128.4984685191837</v>
+        <v>128.1853529991837</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1443715373452399</v>
+        <v>0.146105012885097</v>
       </c>
       <c r="T49">
-        <v>1.356874314375047</v>
+        <v>1.38073625767001</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.366929485253162</v>
+        <v>7.21345178764372</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09812900670025043</v>
+        <v>0.09804824860752373</v>
       </c>
       <c r="C50">
-        <v>368.2373923535359</v>
+        <v>361.5756885718769</v>
       </c>
       <c r="D50">
-        <v>418.0693923535359</v>
+        <v>418.191688571877</v>
       </c>
       <c r="E50">
-        <v>-15.26799999999997</v>
+        <v>-8.48399999999998</v>
       </c>
       <c r="F50">
-        <v>325.632</v>
+        <v>332.416</v>
       </c>
       <c r="G50">
         <v>275.8</v>
@@ -5375,28 +5375,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M50">
-        <v>17.6818176</v>
+        <v>18.0501888</v>
       </c>
       <c r="N50">
-        <v>109.8651211755102</v>
+        <v>109.4967499755102</v>
       </c>
       <c r="O50">
-        <v>16.47976817632653</v>
+        <v>16.42451249632653</v>
       </c>
       <c r="P50">
-        <v>93.38535299918368</v>
+        <v>93.07223747918368</v>
       </c>
       <c r="Q50">
-        <v>128.1853529991837</v>
+        <v>127.8722374791837</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.146105012885097</v>
+        <v>0.1479064678578897</v>
       </c>
       <c r="T50">
-        <v>1.38073625767001</v>
+        <v>1.40553396344713</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.21345178764372</v>
+        <v>7.066238485855074</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09804824860752373</v>
+        <v>0.09796749051479704</v>
       </c>
       <c r="C51">
-        <v>361.5756885718769</v>
+        <v>354.9140563608315</v>
       </c>
       <c r="D51">
-        <v>418.191688571877</v>
+        <v>418.3140563608314</v>
       </c>
       <c r="E51">
-        <v>-8.48399999999998</v>
+        <v>-1.699999999999989</v>
       </c>
       <c r="F51">
-        <v>332.416</v>
+        <v>339.2</v>
       </c>
       <c r="G51">
         <v>275.8</v>
@@ -5457,28 +5457,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M51">
-        <v>18.0501888</v>
+        <v>18.41856</v>
       </c>
       <c r="N51">
-        <v>109.4967499755102</v>
+        <v>109.1283787755102</v>
       </c>
       <c r="O51">
-        <v>16.42451249632653</v>
+        <v>16.36925681632653</v>
       </c>
       <c r="P51">
-        <v>93.07223747918368</v>
+        <v>92.75912195918369</v>
       </c>
       <c r="Q51">
-        <v>127.8722374791837</v>
+        <v>127.5591219591837</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1479064678578897</v>
+        <v>0.1497799810295941</v>
       </c>
       <c r="T51">
-        <v>1.40553396344713</v>
+        <v>1.431323577455334</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.066238485855074</v>
+        <v>6.924913716137973</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09796749051479704</v>
+        <v>0.09788673242207035</v>
       </c>
       <c r="C52">
-        <v>354.9140563608315</v>
+        <v>348.2524957832449</v>
       </c>
       <c r="D52">
-        <v>418.3140563608314</v>
+        <v>418.4364957832449</v>
       </c>
       <c r="E52">
-        <v>-1.699999999999989</v>
+        <v>5.084000000000003</v>
       </c>
       <c r="F52">
-        <v>339.2</v>
+        <v>345.984</v>
       </c>
       <c r="G52">
         <v>275.8</v>
@@ -5539,28 +5539,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M52">
-        <v>18.41856</v>
+        <v>18.7869312</v>
       </c>
       <c r="N52">
-        <v>109.1283787755102</v>
+        <v>108.7600075755102</v>
       </c>
       <c r="O52">
-        <v>16.36925681632653</v>
+        <v>16.31400113632653</v>
       </c>
       <c r="P52">
-        <v>92.75912195918369</v>
+        <v>92.44600643918369</v>
       </c>
       <c r="Q52">
-        <v>127.5591219591837</v>
+        <v>127.2460064391837</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1497799810295941</v>
+        <v>0.1517299641266742</v>
       </c>
       <c r="T52">
-        <v>1.431323577455334</v>
+        <v>1.458165828769996</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.924913716137973</v>
+        <v>6.789131094252915</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09788673242207035</v>
+        <v>0.09780597432934364</v>
       </c>
       <c r="C53">
-        <v>348.2524957832449</v>
+        <v>341.5910069020367</v>
       </c>
       <c r="D53">
-        <v>418.4364957832449</v>
+        <v>418.5590069020366</v>
       </c>
       <c r="E53">
-        <v>5.084000000000003</v>
+        <v>11.86799999999999</v>
       </c>
       <c r="F53">
-        <v>345.984</v>
+        <v>352.768</v>
       </c>
       <c r="G53">
         <v>275.8</v>
@@ -5621,28 +5621,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M53">
-        <v>18.7869312</v>
+        <v>19.1553024</v>
       </c>
       <c r="N53">
-        <v>108.7600075755102</v>
+        <v>108.3916363755102</v>
       </c>
       <c r="O53">
-        <v>16.31400113632653</v>
+        <v>16.25874545632653</v>
       </c>
       <c r="P53">
-        <v>92.44600643918369</v>
+        <v>92.13289091918368</v>
       </c>
       <c r="Q53">
-        <v>127.2460064391837</v>
+        <v>126.9328909191837</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1517299641266742</v>
+        <v>0.1537611965194659</v>
       </c>
       <c r="T53">
-        <v>1.458165828769996</v>
+        <v>1.486126507222768</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.789131094252915</v>
+        <v>6.658570880901896</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09780597432934364</v>
+        <v>0.09772521623661695</v>
       </c>
       <c r="C54">
-        <v>341.5910069020367</v>
+        <v>334.9295897801993</v>
       </c>
       <c r="D54">
-        <v>418.5590069020366</v>
+        <v>418.6815897801993</v>
       </c>
       <c r="E54">
-        <v>11.86799999999999</v>
+        <v>18.65200000000004</v>
       </c>
       <c r="F54">
-        <v>352.768</v>
+        <v>359.552</v>
       </c>
       <c r="G54">
         <v>275.8</v>
@@ -5703,28 +5703,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M54">
-        <v>19.1553024</v>
+        <v>19.5236736</v>
       </c>
       <c r="N54">
-        <v>108.3916363755102</v>
+        <v>108.0232651755102</v>
       </c>
       <c r="O54">
-        <v>16.25874545632653</v>
+        <v>16.20348977632653</v>
       </c>
       <c r="P54">
-        <v>92.13289091918368</v>
+        <v>91.81977539918367</v>
       </c>
       <c r="Q54">
-        <v>126.9328909191837</v>
+        <v>126.6197753991837</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1537611965194659</v>
+        <v>0.1558788643332276</v>
       </c>
       <c r="T54">
-        <v>1.486126507222768</v>
+        <v>1.515277001779914</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.658570880901896</v>
+        <v>6.53293746805469</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09772521623661695</v>
+        <v>0.09764445814389025</v>
       </c>
       <c r="C55">
-        <v>334.9295897801993</v>
+        <v>328.2682444807998</v>
       </c>
       <c r="D55">
-        <v>418.6815897801993</v>
+        <v>418.8042444807998</v>
       </c>
       <c r="E55">
-        <v>18.65200000000004</v>
+        <v>25.43600000000004</v>
       </c>
       <c r="F55">
-        <v>359.552</v>
+        <v>366.336</v>
       </c>
       <c r="G55">
         <v>275.8</v>
@@ -5785,28 +5785,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M55">
-        <v>19.5236736</v>
+        <v>19.8920448</v>
       </c>
       <c r="N55">
-        <v>108.0232651755102</v>
+        <v>107.6548939755102</v>
       </c>
       <c r="O55">
-        <v>16.20348977632653</v>
+        <v>16.14823409632653</v>
       </c>
       <c r="P55">
-        <v>91.81977539918367</v>
+        <v>91.50665987918369</v>
       </c>
       <c r="Q55">
-        <v>126.6197753991837</v>
+        <v>126.3066598791837</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1558788643332276</v>
+        <v>0.158088604660631</v>
       </c>
       <c r="T55">
-        <v>1.515277001779914</v>
+        <v>1.545694909143892</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.53293746805469</v>
+        <v>6.411957144572197</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09764445814389025</v>
+        <v>0.09756370005116356</v>
       </c>
       <c r="C56">
-        <v>328.2682444807998</v>
+        <v>321.6069710669789</v>
       </c>
       <c r="D56">
-        <v>418.8042444807998</v>
+        <v>418.9269710669788</v>
       </c>
       <c r="E56">
-        <v>25.43600000000004</v>
+        <v>32.22000000000003</v>
       </c>
       <c r="F56">
-        <v>366.336</v>
+        <v>373.12</v>
       </c>
       <c r="G56">
         <v>275.8</v>
@@ -5867,28 +5867,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M56">
-        <v>19.8920448</v>
+        <v>20.260416</v>
       </c>
       <c r="N56">
-        <v>107.6548939755102</v>
+        <v>107.2865227755102</v>
       </c>
       <c r="O56">
-        <v>16.14823409632653</v>
+        <v>16.09297841632653</v>
       </c>
       <c r="P56">
-        <v>91.50665987918369</v>
+        <v>91.19354435918368</v>
       </c>
       <c r="Q56">
-        <v>126.3066598791837</v>
+        <v>125.9935443591837</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.158088604660631</v>
+        <v>0.1603965556692524</v>
       </c>
       <c r="T56">
-        <v>1.545694909143892</v>
+        <v>1.577464723501825</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.411957144572197</v>
+        <v>6.295376105579975</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09756370005116356</v>
+        <v>0.09748294195843685</v>
       </c>
       <c r="C57">
-        <v>321.6069710669789</v>
+        <v>314.9457696019509</v>
       </c>
       <c r="D57">
-        <v>418.9269710669788</v>
+        <v>419.0497696019509</v>
       </c>
       <c r="E57">
-        <v>32.22000000000003</v>
+        <v>39.00400000000002</v>
       </c>
       <c r="F57">
-        <v>373.12</v>
+        <v>379.904</v>
       </c>
       <c r="G57">
         <v>275.8</v>
@@ -5949,28 +5949,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M57">
-        <v>20.260416</v>
+        <v>20.6287872</v>
       </c>
       <c r="N57">
-        <v>107.2865227755102</v>
+        <v>106.9181515755102</v>
       </c>
       <c r="O57">
-        <v>16.09297841632653</v>
+        <v>16.03772273632653</v>
       </c>
       <c r="P57">
-        <v>91.19354435918368</v>
+        <v>90.88042883918368</v>
       </c>
       <c r="Q57">
-        <v>125.9935443591837</v>
+        <v>125.6804288391837</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1603965556692524</v>
+        <v>0.162809413541902</v>
       </c>
       <c r="T57">
-        <v>1.577464723501825</v>
+        <v>1.610678620330573</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.295376105579975</v>
+        <v>6.182958675123189</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09748294195843685</v>
+        <v>0.09788668386571016</v>
       </c>
       <c r="C58">
-        <v>314.9457696019509</v>
+        <v>307.5485694223526</v>
       </c>
       <c r="D58">
-        <v>419.0497696019509</v>
+        <v>418.4365694223526</v>
       </c>
       <c r="E58">
-        <v>39.00400000000002</v>
+        <v>45.78800000000007</v>
       </c>
       <c r="F58">
-        <v>379.904</v>
+        <v>386.688</v>
       </c>
       <c r="G58">
         <v>275.8</v>
@@ -6031,45 +6031,45 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M58">
-        <v>20.6287872</v>
+        <v>21.3838464</v>
       </c>
       <c r="N58">
-        <v>106.9181515755102</v>
+        <v>106.1630923755102</v>
       </c>
       <c r="O58">
-        <v>16.03772273632653</v>
+        <v>15.92446385632653</v>
       </c>
       <c r="P58">
-        <v>90.88042883918368</v>
+        <v>90.23862851918369</v>
       </c>
       <c r="Q58">
-        <v>125.6804288391837</v>
+        <v>125.0386285191837</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.162809413541902</v>
+        <v>0.1653344973621167</v>
       </c>
       <c r="T58">
-        <v>1.610678620330573</v>
+        <v>1.64543734956996</v>
       </c>
       <c r="U58">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V58">
         <v>0.15</v>
       </c>
       <c r="W58">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>6.182958675123189</v>
+        <v>5.964639681264742</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09788668386571016</v>
+        <v>0.09781442577298347</v>
       </c>
       <c r="C59">
-        <v>307.5485694223526</v>
+        <v>300.8741825869233</v>
       </c>
       <c r="D59">
-        <v>418.4365694223526</v>
+        <v>418.5461825869232</v>
       </c>
       <c r="E59">
-        <v>45.78800000000007</v>
+        <v>52.57200000000006</v>
       </c>
       <c r="F59">
-        <v>386.688</v>
+        <v>393.472</v>
       </c>
       <c r="G59">
         <v>275.8</v>
@@ -6113,28 +6113,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M59">
-        <v>21.3838464</v>
+        <v>21.7590016</v>
       </c>
       <c r="N59">
-        <v>106.1630923755102</v>
+        <v>105.7879371755102</v>
       </c>
       <c r="O59">
-        <v>15.92446385632653</v>
+        <v>15.86819057632653</v>
       </c>
       <c r="P59">
-        <v>90.23862851918369</v>
+        <v>89.91974659918368</v>
       </c>
       <c r="Q59">
-        <v>125.0386285191837</v>
+        <v>124.7197465991837</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1653344973621167</v>
+        <v>0.1679798232690083</v>
       </c>
       <c r="T59">
-        <v>1.64543734956996</v>
+        <v>1.681851256392175</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.964639681264742</v>
+        <v>5.861801066070522</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09781442577298345</v>
+        <v>0.09774216768025674</v>
       </c>
       <c r="C60">
-        <v>300.8741825869233</v>
+        <v>294.1998531948196</v>
       </c>
       <c r="D60">
-        <v>418.5461825869232</v>
+        <v>418.6558531948197</v>
       </c>
       <c r="E60">
-        <v>52.572</v>
+        <v>59.35599999999999</v>
       </c>
       <c r="F60">
-        <v>393.472</v>
+        <v>400.256</v>
       </c>
       <c r="G60">
         <v>275.8</v>
@@ -6195,28 +6195,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M60">
-        <v>21.7590016</v>
+        <v>22.1341568</v>
       </c>
       <c r="N60">
-        <v>105.7879371755102</v>
+        <v>105.4127819755102</v>
       </c>
       <c r="O60">
-        <v>15.86819057632653</v>
+        <v>15.81191729632653</v>
       </c>
       <c r="P60">
-        <v>89.91974659918368</v>
+        <v>89.60086467918369</v>
       </c>
       <c r="Q60">
-        <v>124.7197465991837</v>
+        <v>124.4008646791837</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1679798232690082</v>
+        <v>0.1707541894640409</v>
       </c>
       <c r="T60">
-        <v>1.681851256392175</v>
+        <v>1.720041451352059</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.861801066070522</v>
+        <v>5.76244850562865</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09774216768025674</v>
+        <v>0.09766990958753005</v>
       </c>
       <c r="C61">
-        <v>294.1998531948196</v>
+        <v>287.5255812912092</v>
       </c>
       <c r="D61">
-        <v>418.6558531948197</v>
+        <v>418.7655812912091</v>
       </c>
       <c r="E61">
-        <v>59.35599999999999</v>
+        <v>66.13999999999999</v>
       </c>
       <c r="F61">
-        <v>400.256</v>
+        <v>407.04</v>
       </c>
       <c r="G61">
         <v>275.8</v>
@@ -6277,28 +6277,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M61">
-        <v>22.1341568</v>
+        <v>22.509312</v>
       </c>
       <c r="N61">
-        <v>105.4127819755102</v>
+        <v>105.0376267755102</v>
       </c>
       <c r="O61">
-        <v>15.81191729632653</v>
+        <v>15.75564401632653</v>
       </c>
       <c r="P61">
-        <v>89.60086467918369</v>
+        <v>89.28198275918369</v>
       </c>
       <c r="Q61">
-        <v>124.4008646791837</v>
+        <v>124.0819827591837</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1707541894640409</v>
+        <v>0.1736672739688251</v>
       </c>
       <c r="T61">
-        <v>1.720041451352059</v>
+        <v>1.760141156059938</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.76244850562865</v>
+        <v>5.666407697201506</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09766990958753005</v>
+        <v>0.09759765149480337</v>
       </c>
       <c r="C62">
-        <v>287.5255812912092</v>
+        <v>280.8513669213058</v>
       </c>
       <c r="D62">
-        <v>418.7655812912091</v>
+        <v>418.8753669213058</v>
       </c>
       <c r="E62">
-        <v>66.13999999999999</v>
+        <v>72.92399999999998</v>
       </c>
       <c r="F62">
-        <v>407.04</v>
+        <v>413.824</v>
       </c>
       <c r="G62">
         <v>275.8</v>
@@ -6359,28 +6359,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M62">
-        <v>22.509312</v>
+        <v>22.8844672</v>
       </c>
       <c r="N62">
-        <v>105.0376267755102</v>
+        <v>104.6624715755102</v>
       </c>
       <c r="O62">
-        <v>15.75564401632653</v>
+        <v>15.69937073632653</v>
       </c>
       <c r="P62">
-        <v>89.28198275918369</v>
+        <v>88.96310083918368</v>
       </c>
       <c r="Q62">
-        <v>124.0819827591837</v>
+        <v>123.7631008391837</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1736672739688251</v>
+        <v>0.1767297474225727</v>
       </c>
       <c r="T62">
-        <v>1.760141156059938</v>
+        <v>1.802297255881041</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.666407697201506</v>
+        <v>5.573515767739186</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09759765149480337</v>
+        <v>0.09752539340207667</v>
       </c>
       <c r="C63">
-        <v>280.8513669213058</v>
+        <v>274.1772101303717</v>
       </c>
       <c r="D63">
-        <v>418.8753669213058</v>
+        <v>418.9852101303718</v>
       </c>
       <c r="E63">
-        <v>72.92399999999998</v>
+        <v>79.70800000000003</v>
       </c>
       <c r="F63">
-        <v>413.824</v>
+        <v>420.608</v>
       </c>
       <c r="G63">
         <v>275.8</v>
@@ -6441,28 +6441,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M63">
-        <v>22.8844672</v>
+        <v>23.2596224</v>
       </c>
       <c r="N63">
-        <v>104.6624715755102</v>
+        <v>104.2873163755102</v>
       </c>
       <c r="O63">
-        <v>15.69937073632653</v>
+        <v>15.64309745632653</v>
       </c>
       <c r="P63">
-        <v>88.96310083918368</v>
+        <v>88.64421891918369</v>
       </c>
       <c r="Q63">
-        <v>123.7631008391837</v>
+        <v>123.4442189191837</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1767297474225727</v>
+        <v>0.1799534036896754</v>
       </c>
       <c r="T63">
-        <v>1.802297255881041</v>
+        <v>1.846672097797992</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.573515767739186</v>
+        <v>5.483620352130489</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09752539340207667</v>
+        <v>0.09745313530934996</v>
       </c>
       <c r="C64">
-        <v>274.1772101303717</v>
+        <v>267.5031109637162</v>
       </c>
       <c r="D64">
-        <v>418.9852101303718</v>
+        <v>419.0951109637163</v>
       </c>
       <c r="E64">
-        <v>79.70800000000003</v>
+        <v>86.49200000000002</v>
       </c>
       <c r="F64">
-        <v>420.608</v>
+        <v>427.392</v>
       </c>
       <c r="G64">
         <v>275.8</v>
@@ -6523,28 +6523,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M64">
-        <v>23.2596224</v>
+        <v>23.6347776</v>
       </c>
       <c r="N64">
-        <v>104.2873163755102</v>
+        <v>103.9121611755102</v>
       </c>
       <c r="O64">
-        <v>15.64309745632653</v>
+        <v>15.58682417632653</v>
       </c>
       <c r="P64">
-        <v>88.64421891918369</v>
+        <v>88.32533699918369</v>
       </c>
       <c r="Q64">
-        <v>123.4442189191837</v>
+        <v>123.1253369991837</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1799534036896754</v>
+        <v>0.1833513116468918</v>
       </c>
       <c r="T64">
-        <v>1.846672097797992</v>
+        <v>1.893445579818561</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.483620352130489</v>
+        <v>5.39657875923953</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09745313530934996</v>
+        <v>0.09738087721662327</v>
       </c>
       <c r="C65">
-        <v>267.5031109637162</v>
+        <v>260.8290694666961</v>
       </c>
       <c r="D65">
-        <v>419.0951109637163</v>
+        <v>419.205069466696</v>
       </c>
       <c r="E65">
-        <v>86.49200000000002</v>
+        <v>93.27600000000001</v>
       </c>
       <c r="F65">
-        <v>427.392</v>
+        <v>434.176</v>
       </c>
       <c r="G65">
         <v>275.8</v>
@@ -6605,28 +6605,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M65">
-        <v>23.6347776</v>
+        <v>24.0099328</v>
       </c>
       <c r="N65">
-        <v>103.9121611755102</v>
+        <v>103.5370059755102</v>
       </c>
       <c r="O65">
-        <v>15.58682417632653</v>
+        <v>15.53055089632653</v>
       </c>
       <c r="P65">
-        <v>88.32533699918369</v>
+        <v>88.00645507918368</v>
       </c>
       <c r="Q65">
-        <v>123.1253369991837</v>
+        <v>122.8064550791837</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1833513116468918</v>
+        <v>0.186937992268398</v>
       </c>
       <c r="T65">
-        <v>1.893445579818561</v>
+        <v>1.942817588618051</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.39657875923953</v>
+        <v>5.312257216126411</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09738087721662327</v>
+        <v>0.09730861912389659</v>
       </c>
       <c r="C66">
-        <v>260.8290694666961</v>
+        <v>254.1550856847156</v>
       </c>
       <c r="D66">
-        <v>419.205069466696</v>
+        <v>419.3150856847156</v>
       </c>
       <c r="E66">
-        <v>93.27600000000001</v>
+        <v>100.06</v>
       </c>
       <c r="F66">
-        <v>434.176</v>
+        <v>440.96</v>
       </c>
       <c r="G66">
         <v>275.8</v>
@@ -6687,28 +6687,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M66">
-        <v>24.0099328</v>
+        <v>24.385088</v>
       </c>
       <c r="N66">
-        <v>103.5370059755102</v>
+        <v>103.1618507755102</v>
       </c>
       <c r="O66">
-        <v>15.53055089632653</v>
+        <v>15.47427761632653</v>
       </c>
       <c r="P66">
-        <v>88.00645507918368</v>
+        <v>87.68757315918369</v>
       </c>
       <c r="Q66">
-        <v>122.8064550791837</v>
+        <v>122.4875731591837</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.186937992268398</v>
+        <v>0.190729626068276</v>
       </c>
       <c r="T66">
-        <v>1.942817588618051</v>
+        <v>1.995010855063227</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.312257216126411</v>
+        <v>5.230530182032159</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09730861912389659</v>
+        <v>0.09723636103116988</v>
       </c>
       <c r="C67">
-        <v>254.1550856847156</v>
+        <v>247.4811596632271</v>
       </c>
       <c r="D67">
-        <v>419.3150856847156</v>
+        <v>419.4251596632271</v>
       </c>
       <c r="E67">
-        <v>100.06</v>
+        <v>106.8440000000001</v>
       </c>
       <c r="F67">
-        <v>440.96</v>
+        <v>447.744</v>
       </c>
       <c r="G67">
         <v>275.8</v>
@@ -6769,28 +6769,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M67">
-        <v>24.385088</v>
+        <v>24.7602432</v>
       </c>
       <c r="N67">
-        <v>103.1618507755102</v>
+        <v>102.7866955755102</v>
       </c>
       <c r="O67">
-        <v>15.47427761632653</v>
+        <v>15.41800433632653</v>
       </c>
       <c r="P67">
-        <v>87.68757315918369</v>
+        <v>87.36869123918368</v>
       </c>
       <c r="Q67">
-        <v>122.4875731591837</v>
+        <v>122.1686912391837</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.190729626068276</v>
+        <v>0.1947442971504997</v>
       </c>
       <c r="T67">
-        <v>1.995010855063227</v>
+        <v>2.050274313652236</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.230530182032159</v>
+        <v>5.151279724728641</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09723636103116988</v>
+        <v>0.09716410293844319</v>
       </c>
       <c r="C68">
-        <v>247.4811596632271</v>
+        <v>240.8072914477304</v>
       </c>
       <c r="D68">
-        <v>419.4251596632271</v>
+        <v>419.5352914477305</v>
       </c>
       <c r="E68">
-        <v>106.8440000000001</v>
+        <v>113.628</v>
       </c>
       <c r="F68">
-        <v>447.744</v>
+        <v>454.528</v>
       </c>
       <c r="G68">
         <v>275.8</v>
@@ -6851,28 +6851,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M68">
-        <v>24.7602432</v>
+        <v>25.1353984</v>
       </c>
       <c r="N68">
-        <v>102.7866955755102</v>
+        <v>102.4115403755102</v>
       </c>
       <c r="O68">
-        <v>15.41800433632653</v>
+        <v>15.36173105632653</v>
       </c>
       <c r="P68">
-        <v>87.36869123918368</v>
+        <v>87.04980931918368</v>
       </c>
       <c r="Q68">
-        <v>122.1686912391837</v>
+        <v>121.8498093191837</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1947442971504997</v>
+        <v>0.199002281631646</v>
       </c>
       <c r="T68">
-        <v>2.050274313652236</v>
+        <v>2.108887072761791</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.151279724728641</v>
+        <v>5.074394952717766</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09716410293844319</v>
+        <v>0.09709184484571648</v>
       </c>
       <c r="C69">
-        <v>240.8072914477304</v>
+        <v>234.1334810837734</v>
       </c>
       <c r="D69">
-        <v>419.5352914477305</v>
+        <v>419.6454810837734</v>
       </c>
       <c r="E69">
-        <v>113.628</v>
+        <v>120.412</v>
       </c>
       <c r="F69">
-        <v>454.528</v>
+        <v>461.312</v>
       </c>
       <c r="G69">
         <v>275.8</v>
@@ -6933,28 +6933,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M69">
-        <v>25.1353984</v>
+        <v>25.5105536</v>
       </c>
       <c r="N69">
-        <v>102.4115403755102</v>
+        <v>102.0363851755102</v>
       </c>
       <c r="O69">
-        <v>15.36173105632653</v>
+        <v>15.30545777632653</v>
       </c>
       <c r="P69">
-        <v>87.04980931918368</v>
+        <v>86.73092739918368</v>
       </c>
       <c r="Q69">
-        <v>121.8498093191837</v>
+        <v>121.5309273991837</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.199002281631646</v>
+        <v>0.203526390142864</v>
       </c>
       <c r="T69">
-        <v>2.108887072761791</v>
+        <v>2.171163129315693</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.074394952717766</v>
+        <v>4.99977149753074</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09709184484571648</v>
+        <v>0.09701958675298979</v>
       </c>
       <c r="C70">
-        <v>234.1334810837734</v>
+        <v>227.4597286169515</v>
       </c>
       <c r="D70">
-        <v>419.6454810837734</v>
+        <v>419.7557286169514</v>
       </c>
       <c r="E70">
-        <v>120.412</v>
+        <v>127.196</v>
       </c>
       <c r="F70">
-        <v>461.312</v>
+        <v>468.096</v>
       </c>
       <c r="G70">
         <v>275.8</v>
@@ -7015,28 +7015,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M70">
-        <v>25.5105536</v>
+        <v>25.8857088</v>
       </c>
       <c r="N70">
-        <v>102.0363851755102</v>
+        <v>101.6612299755102</v>
       </c>
       <c r="O70">
-        <v>15.30545777632653</v>
+        <v>15.24918449632653</v>
       </c>
       <c r="P70">
-        <v>86.73092739918368</v>
+        <v>86.41204547918367</v>
       </c>
       <c r="Q70">
-        <v>121.5309273991837</v>
+        <v>121.2120454791837</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.203526390142864</v>
+        <v>0.2083423766225477</v>
       </c>
       <c r="T70">
-        <v>2.171163129315693</v>
+        <v>2.237456995969847</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.99977149753074</v>
+        <v>4.927311041044787</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09701958675298979</v>
+        <v>0.09694732866026308</v>
       </c>
       <c r="C71">
-        <v>227.4597286169515</v>
+        <v>220.7860340929081</v>
       </c>
       <c r="D71">
-        <v>419.7557286169514</v>
+        <v>419.8660340929081</v>
       </c>
       <c r="E71">
-        <v>127.196</v>
+        <v>133.9800000000001</v>
       </c>
       <c r="F71">
-        <v>468.096</v>
+        <v>474.8800000000001</v>
       </c>
       <c r="G71">
         <v>275.8</v>
@@ -7097,28 +7097,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M71">
-        <v>25.8857088</v>
+        <v>26.26086400000001</v>
       </c>
       <c r="N71">
-        <v>101.6612299755102</v>
+        <v>101.2860747755102</v>
       </c>
       <c r="O71">
-        <v>15.24918449632653</v>
+        <v>15.19291121632653</v>
       </c>
       <c r="P71">
-        <v>86.41204547918367</v>
+        <v>86.09316355918367</v>
       </c>
       <c r="Q71">
-        <v>121.2120454791837</v>
+        <v>120.8931635591837</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2083423766225477</v>
+        <v>0.2134794288675436</v>
       </c>
       <c r="T71">
-        <v>2.237456995969847</v>
+        <v>2.308170453734278</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.927311041044787</v>
+        <v>4.856920883315575</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09694732866026308</v>
+        <v>0.0968750705675364</v>
       </c>
       <c r="C72">
-        <v>220.7860340929081</v>
+        <v>214.1123975573348</v>
       </c>
       <c r="D72">
-        <v>419.8660340929081</v>
+        <v>419.9763975573347</v>
       </c>
       <c r="E72">
-        <v>133.9800000000001</v>
+        <v>140.7640000000001</v>
       </c>
       <c r="F72">
-        <v>474.8800000000001</v>
+        <v>481.664</v>
       </c>
       <c r="G72">
         <v>275.8</v>
@@ -7179,28 +7179,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M72">
-        <v>26.26086400000001</v>
+        <v>26.6360192</v>
       </c>
       <c r="N72">
-        <v>101.2860747755102</v>
+        <v>100.9109195755102</v>
       </c>
       <c r="O72">
-        <v>15.19291121632653</v>
+        <v>15.13663793632653</v>
       </c>
       <c r="P72">
-        <v>86.09316355918367</v>
+        <v>85.77428163918367</v>
       </c>
       <c r="Q72">
-        <v>120.8931635591837</v>
+        <v>120.5742816391837</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2134794288675436</v>
+        <v>0.2189707605777118</v>
       </c>
       <c r="T72">
-        <v>2.308170453734278</v>
+        <v>2.38376070168936</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.856920883315575</v>
+        <v>4.788513546930849</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09687507056753639</v>
+        <v>0.09680281247480968</v>
       </c>
       <c r="C73">
-        <v>214.1123975573348</v>
+        <v>207.4388190559711</v>
       </c>
       <c r="D73">
-        <v>419.9763975573347</v>
+        <v>420.086819055971</v>
       </c>
       <c r="E73">
-        <v>140.764</v>
+        <v>147.548</v>
       </c>
       <c r="F73">
-        <v>481.664</v>
+        <v>488.448</v>
       </c>
       <c r="G73">
         <v>275.8</v>
@@ -7261,28 +7261,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M73">
-        <v>26.6360192</v>
+        <v>27.0111744</v>
       </c>
       <c r="N73">
-        <v>100.9109195755102</v>
+        <v>100.5357643755102</v>
       </c>
       <c r="O73">
-        <v>15.13663793632653</v>
+        <v>15.08036465632653</v>
       </c>
       <c r="P73">
-        <v>85.77428163918367</v>
+        <v>85.45539971918367</v>
       </c>
       <c r="Q73">
-        <v>120.5742816391837</v>
+        <v>120.2553997191837</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2189707605777117</v>
+        <v>0.2248543302671775</v>
       </c>
       <c r="T73">
-        <v>2.383760701689359</v>
+        <v>2.464750253069803</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.788513546930849</v>
+        <v>4.722006414334588</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09680281247480968</v>
+        <v>0.096730554382083</v>
       </c>
       <c r="C74">
-        <v>207.4388190559711</v>
+        <v>200.7652986346045</v>
       </c>
       <c r="D74">
-        <v>420.086819055971</v>
+        <v>420.1972986346045</v>
       </c>
       <c r="E74">
-        <v>147.548</v>
+        <v>154.332</v>
       </c>
       <c r="F74">
-        <v>488.448</v>
+        <v>495.232</v>
       </c>
       <c r="G74">
         <v>275.8</v>
@@ -7343,28 +7343,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M74">
-        <v>27.0111744</v>
+        <v>27.3863296</v>
       </c>
       <c r="N74">
-        <v>100.5357643755102</v>
+        <v>100.1606091755102</v>
       </c>
       <c r="O74">
-        <v>15.08036465632653</v>
+        <v>15.02409137632653</v>
       </c>
       <c r="P74">
-        <v>85.45539971918367</v>
+        <v>85.13651779918368</v>
       </c>
       <c r="Q74">
-        <v>120.2553997191837</v>
+        <v>119.9365177991837</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2248543302671775</v>
+        <v>0.2311737199336407</v>
       </c>
       <c r="T74">
-        <v>2.464750253069803</v>
+        <v>2.551739030478429</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.722006414334588</v>
+        <v>4.657321394960142</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.096730554382083</v>
+        <v>0.09665829628935629</v>
       </c>
       <c r="C75">
-        <v>200.7652986346045</v>
+        <v>194.0918363390709</v>
       </c>
       <c r="D75">
-        <v>420.1972986346045</v>
+        <v>420.3078363390709</v>
       </c>
       <c r="E75">
-        <v>154.332</v>
+        <v>161.116</v>
       </c>
       <c r="F75">
-        <v>495.232</v>
+        <v>502.016</v>
       </c>
       <c r="G75">
         <v>275.8</v>
@@ -7425,28 +7425,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M75">
-        <v>27.3863296</v>
+        <v>27.7614848</v>
       </c>
       <c r="N75">
-        <v>100.1606091755102</v>
+        <v>99.78545397551022</v>
       </c>
       <c r="O75">
-        <v>15.02409137632653</v>
+        <v>14.96781809632653</v>
       </c>
       <c r="P75">
-        <v>85.13651779918368</v>
+        <v>84.81763587918368</v>
       </c>
       <c r="Q75">
-        <v>119.9365177991837</v>
+        <v>119.6176358791837</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2311737199336407</v>
+        <v>0.2379792164975242</v>
       </c>
       <c r="T75">
-        <v>2.551739030478429</v>
+        <v>2.645419252303102</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.657321394960142</v>
+        <v>4.594384619352573</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09665829628935629</v>
+        <v>0.09658603819662959</v>
       </c>
       <c r="C76">
-        <v>194.0918363390709</v>
+        <v>187.4184322152546</v>
       </c>
       <c r="D76">
-        <v>420.3078363390709</v>
+        <v>420.4184322152545</v>
       </c>
       <c r="E76">
-        <v>161.116</v>
+        <v>167.9</v>
       </c>
       <c r="F76">
-        <v>502.016</v>
+        <v>508.8</v>
       </c>
       <c r="G76">
         <v>275.8</v>
@@ -7507,28 +7507,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M76">
-        <v>27.7614848</v>
+        <v>28.13664</v>
       </c>
       <c r="N76">
-        <v>99.78545397551022</v>
+        <v>99.41029877551021</v>
       </c>
       <c r="O76">
-        <v>14.96781809632653</v>
+        <v>14.91154481632653</v>
       </c>
       <c r="P76">
-        <v>84.81763587918368</v>
+        <v>84.49875395918369</v>
       </c>
       <c r="Q76">
-        <v>119.6176358791837</v>
+        <v>119.2987539591837</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2379792164975242</v>
+        <v>0.2453291527865184</v>
       </c>
       <c r="T76">
-        <v>2.645419252303102</v>
+        <v>2.746593891873749</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.594384619352573</v>
+        <v>4.533126157761204</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09658603819662959</v>
+        <v>0.0981287801039029</v>
       </c>
       <c r="C77">
-        <v>187.4184322152546</v>
+        <v>178.2857354002092</v>
       </c>
       <c r="D77">
-        <v>420.4184322152545</v>
+        <v>418.0697354002091</v>
       </c>
       <c r="E77">
-        <v>167.9</v>
+        <v>174.684</v>
       </c>
       <c r="F77">
-        <v>508.8</v>
+        <v>515.5839999999999</v>
       </c>
       <c r="G77">
         <v>275.8</v>
@@ -7589,45 +7589,45 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M77">
-        <v>28.13664</v>
+        <v>29.8007552</v>
       </c>
       <c r="N77">
-        <v>99.41029877551021</v>
+        <v>97.74618357551022</v>
       </c>
       <c r="O77">
-        <v>14.91154481632653</v>
+        <v>14.66192753632653</v>
       </c>
       <c r="P77">
-        <v>84.49875395918369</v>
+        <v>83.08425603918369</v>
       </c>
       <c r="Q77">
-        <v>119.2987539591837</v>
+        <v>117.8842560391837</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2453291527865184</v>
+        <v>0.2532915837662621</v>
       </c>
       <c r="T77">
-        <v>2.746593891873749</v>
+        <v>2.856199751408618</v>
       </c>
       <c r="U77">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V77">
         <v>0.15</v>
       </c>
       <c r="W77">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>4.533126157761204</v>
+        <v>4.27999015191099</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0981287801039029</v>
+        <v>0.09807777201117619</v>
       </c>
       <c r="C78">
-        <v>178.2857354002092</v>
+        <v>171.5789714358139</v>
       </c>
       <c r="D78">
-        <v>418.0697354002091</v>
+        <v>418.1469714358138</v>
       </c>
       <c r="E78">
-        <v>174.684</v>
+        <v>181.468</v>
       </c>
       <c r="F78">
-        <v>515.5839999999999</v>
+        <v>522.3679999999999</v>
       </c>
       <c r="G78">
         <v>275.8</v>
@@ -7671,28 +7671,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M78">
-        <v>29.8007552</v>
+        <v>30.1928704</v>
       </c>
       <c r="N78">
-        <v>97.74618357551022</v>
+        <v>97.35406837551021</v>
       </c>
       <c r="O78">
-        <v>14.66192753632653</v>
+        <v>14.60311025632653</v>
       </c>
       <c r="P78">
-        <v>83.08425603918369</v>
+        <v>82.75095811918368</v>
       </c>
       <c r="Q78">
-        <v>117.8842560391837</v>
+        <v>117.5509581191837</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2532915837662621</v>
+        <v>0.2619464000485922</v>
       </c>
       <c r="T78">
-        <v>2.856199751408618</v>
+        <v>2.975336555250865</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.27999015191099</v>
+        <v>4.224405864223834</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09807777201117619</v>
+        <v>0.0980267639184495</v>
       </c>
       <c r="C79">
-        <v>171.5789714358139</v>
+        <v>164.8722360145391</v>
       </c>
       <c r="D79">
-        <v>418.1469714358138</v>
+        <v>418.2242360145392</v>
       </c>
       <c r="E79">
-        <v>181.468</v>
+        <v>188.2520000000001</v>
       </c>
       <c r="F79">
-        <v>522.3679999999999</v>
+        <v>529.152</v>
       </c>
       <c r="G79">
         <v>275.8</v>
@@ -7753,28 +7753,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M79">
-        <v>30.1928704</v>
+        <v>30.5849856</v>
       </c>
       <c r="N79">
-        <v>97.35406837551021</v>
+        <v>96.96195317551022</v>
       </c>
       <c r="O79">
-        <v>14.60311025632653</v>
+        <v>14.54429297632653</v>
       </c>
       <c r="P79">
-        <v>82.75095811918368</v>
+        <v>82.41766019918369</v>
       </c>
       <c r="Q79">
-        <v>117.5509581191837</v>
+        <v>117.2176601991837</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2619464000485922</v>
+        <v>0.2713880178111341</v>
       </c>
       <c r="T79">
-        <v>2.975336555250865</v>
+        <v>3.105303977624226</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.224405864223834</v>
+        <v>4.170246814682502</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0980267639184495</v>
+        <v>0.09797575582572279</v>
       </c>
       <c r="C80">
-        <v>164.8722360145391</v>
+        <v>158.1655291522108</v>
       </c>
       <c r="D80">
-        <v>418.2242360145392</v>
+        <v>418.3015291522107</v>
       </c>
       <c r="E80">
-        <v>188.2520000000001</v>
+        <v>195.0360000000001</v>
       </c>
       <c r="F80">
-        <v>529.152</v>
+        <v>535.936</v>
       </c>
       <c r="G80">
         <v>275.8</v>
@@ -7835,28 +7835,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M80">
-        <v>30.5849856</v>
+        <v>30.97710080000001</v>
       </c>
       <c r="N80">
-        <v>96.96195317551022</v>
+        <v>96.56983797551021</v>
       </c>
       <c r="O80">
-        <v>14.54429297632653</v>
+        <v>14.48547569632653</v>
       </c>
       <c r="P80">
-        <v>82.41766019918369</v>
+        <v>82.08436227918368</v>
       </c>
       <c r="Q80">
-        <v>117.2176601991837</v>
+        <v>116.8843622791837</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2713880178111341</v>
+        <v>0.2817288372653467</v>
       </c>
       <c r="T80">
-        <v>3.105303977624226</v>
+        <v>3.247649249747432</v>
       </c>
       <c r="U80">
         <v>0.0578</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.170246814682502</v>
+        <v>4.117458880319433</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09797575582572279</v>
+        <v>0.09792474773299609</v>
       </c>
       <c r="C81">
-        <v>158.1655291522108</v>
+        <v>151.4588508646656</v>
       </c>
       <c r="D81">
-        <v>418.3015291522107</v>
+        <v>418.3788508646656</v>
       </c>
       <c r="E81">
-        <v>195.0360000000001</v>
+        <v>201.8200000000001</v>
       </c>
       <c r="F81">
-        <v>535.936</v>
+        <v>542.72</v>
       </c>
       <c r="G81">
         <v>275.8</v>
@@ -7917,28 +7917,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M81">
-        <v>30.97710080000001</v>
+        <v>31.36921600000001</v>
       </c>
       <c r="N81">
-        <v>96.56983797551021</v>
+        <v>96.1777227755102</v>
       </c>
       <c r="O81">
-        <v>14.48547569632653</v>
+        <v>14.42665841632653</v>
       </c>
       <c r="P81">
-        <v>82.08436227918368</v>
+        <v>81.75106435918367</v>
       </c>
       <c r="Q81">
-        <v>116.8843622791837</v>
+        <v>116.5510643591837</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2817288372653467</v>
+        <v>0.2931037386649805</v>
       </c>
       <c r="T81">
-        <v>3.247649249747432</v>
+        <v>3.404229049082957</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.117458880319433</v>
+        <v>4.065990644315439</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09792474773299609</v>
+        <v>0.09787373964026941</v>
       </c>
       <c r="C82">
-        <v>151.4588508646656</v>
+        <v>144.7522011677523</v>
       </c>
       <c r="D82">
-        <v>418.3788508646656</v>
+        <v>418.4562011677524</v>
       </c>
       <c r="E82">
-        <v>201.8200000000001</v>
+        <v>208.604</v>
       </c>
       <c r="F82">
-        <v>542.72</v>
+        <v>549.504</v>
       </c>
       <c r="G82">
         <v>275.8</v>
@@ -7999,28 +7999,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M82">
-        <v>31.36921600000001</v>
+        <v>31.7613312</v>
       </c>
       <c r="N82">
-        <v>96.1777227755102</v>
+        <v>95.78560757551021</v>
       </c>
       <c r="O82">
-        <v>14.42665841632653</v>
+        <v>14.36784113632653</v>
       </c>
       <c r="P82">
-        <v>81.75106435918367</v>
+        <v>81.41776643918368</v>
       </c>
       <c r="Q82">
-        <v>116.5510643591837</v>
+        <v>116.2177664391837</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2931037386649805</v>
+        <v>0.3056759981066812</v>
       </c>
       <c r="T82">
-        <v>3.404229049082957</v>
+        <v>3.577290932559066</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.065990644315439</v>
+        <v>4.015793228953521</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09787373964026941</v>
+        <v>0.1002622315475427</v>
       </c>
       <c r="C83">
-        <v>144.7522011677523</v>
+        <v>134.3766388574953</v>
       </c>
       <c r="D83">
-        <v>418.4562011677524</v>
+        <v>414.8646388574953</v>
       </c>
       <c r="E83">
-        <v>208.604</v>
+        <v>215.388</v>
       </c>
       <c r="F83">
-        <v>549.504</v>
+        <v>556.288</v>
       </c>
       <c r="G83">
         <v>275.8</v>
@@ -8081,45 +8081,45 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M83">
-        <v>31.7613312</v>
+        <v>34.1004544</v>
       </c>
       <c r="N83">
-        <v>95.78560757551021</v>
+        <v>93.44648437551021</v>
       </c>
       <c r="O83">
-        <v>14.36784113632653</v>
+        <v>14.01697265632653</v>
       </c>
       <c r="P83">
-        <v>81.41776643918368</v>
+        <v>79.42951171918368</v>
       </c>
       <c r="Q83">
-        <v>116.2177664391837</v>
+        <v>114.2295117191837</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3056759981066812</v>
+        <v>0.3196451752641262</v>
       </c>
       <c r="T83">
-        <v>3.577290932559066</v>
+        <v>3.769581914199184</v>
       </c>
       <c r="U83">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V83">
         <v>0.15</v>
       </c>
       <c r="W83">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.015793228953521</v>
+        <v>3.740329594420601</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1002622315475427</v>
+        <v>0.100240973454816</v>
       </c>
       <c r="C84">
-        <v>134.3766388574953</v>
+        <v>127.624332599348</v>
       </c>
       <c r="D84">
-        <v>414.8646388574953</v>
+        <v>414.896332599348</v>
       </c>
       <c r="E84">
-        <v>215.388</v>
+        <v>222.172</v>
       </c>
       <c r="F84">
-        <v>556.288</v>
+        <v>563.072</v>
       </c>
       <c r="G84">
         <v>275.8</v>
@@ -8163,28 +8163,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M84">
-        <v>34.1004544</v>
+        <v>34.5163136</v>
       </c>
       <c r="N84">
-        <v>93.44648437551021</v>
+        <v>93.03062517551021</v>
       </c>
       <c r="O84">
-        <v>14.01697265632653</v>
+        <v>13.95459377632653</v>
       </c>
       <c r="P84">
-        <v>79.42951171918368</v>
+        <v>79.07603139918368</v>
       </c>
       <c r="Q84">
-        <v>114.2295117191837</v>
+        <v>113.8760313991837</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3196451752641262</v>
+        <v>0.3352577850283296</v>
       </c>
       <c r="T84">
-        <v>3.769581914199184</v>
+        <v>3.984495364267554</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.740329594420601</v>
+        <v>3.69526538243963</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.100240973454816</v>
+        <v>0.1002197153620893</v>
       </c>
       <c r="C85">
-        <v>127.624332599348</v>
+        <v>120.8720311840816</v>
       </c>
       <c r="D85">
-        <v>414.896332599348</v>
+        <v>414.9280311840815</v>
       </c>
       <c r="E85">
-        <v>222.172</v>
+        <v>228.956</v>
       </c>
       <c r="F85">
-        <v>563.072</v>
+        <v>569.856</v>
       </c>
       <c r="G85">
         <v>275.8</v>
@@ -8245,28 +8245,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M85">
-        <v>34.5163136</v>
+        <v>34.9321728</v>
       </c>
       <c r="N85">
-        <v>93.03062517551021</v>
+        <v>92.61476597551021</v>
       </c>
       <c r="O85">
-        <v>13.95459377632653</v>
+        <v>13.89221489632653</v>
       </c>
       <c r="P85">
-        <v>79.07603139918368</v>
+        <v>78.72255107918367</v>
       </c>
       <c r="Q85">
-        <v>113.8760313991837</v>
+        <v>113.5225510791837</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3352577850283296</v>
+        <v>0.3528219710130584</v>
       </c>
       <c r="T85">
-        <v>3.984495364267554</v>
+        <v>4.226272995594469</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.69526538243963</v>
+        <v>3.651274127886778</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1002197153620893</v>
+        <v>0.1001984572693626</v>
       </c>
       <c r="C86">
-        <v>120.8720311840816</v>
+        <v>114.1197346128062</v>
       </c>
       <c r="D86">
-        <v>414.9280311840815</v>
+        <v>414.9597346128061</v>
       </c>
       <c r="E86">
-        <v>228.956</v>
+        <v>235.74</v>
       </c>
       <c r="F86">
-        <v>569.856</v>
+        <v>576.64</v>
       </c>
       <c r="G86">
         <v>275.8</v>
@@ -8327,28 +8327,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M86">
-        <v>34.9321728</v>
+        <v>35.348032</v>
       </c>
       <c r="N86">
-        <v>92.61476597551021</v>
+        <v>92.19890677551021</v>
       </c>
       <c r="O86">
-        <v>13.89221489632653</v>
+        <v>13.82983601632653</v>
       </c>
       <c r="P86">
-        <v>78.72255107918367</v>
+        <v>78.36907075918367</v>
       </c>
       <c r="Q86">
-        <v>113.5225510791837</v>
+        <v>113.1690707591837</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3528219710130582</v>
+        <v>0.3727280484624174</v>
       </c>
       <c r="T86">
-        <v>4.226272995594466</v>
+        <v>4.500287644431636</v>
       </c>
       <c r="U86">
         <v>0.0613</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.651274127886778</v>
+        <v>3.608317961676345</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1001984572693626</v>
+        <v>0.1001771991766359</v>
       </c>
       <c r="C87">
-        <v>114.1197346128062</v>
+        <v>107.3674428866321</v>
       </c>
       <c r="D87">
-        <v>414.9597346128061</v>
+        <v>414.9914428866321</v>
       </c>
       <c r="E87">
-        <v>235.74</v>
+        <v>242.524</v>
       </c>
       <c r="F87">
-        <v>576.64</v>
+        <v>583.424</v>
       </c>
       <c r="G87">
         <v>275.8</v>
@@ -8409,28 +8409,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M87">
-        <v>35.348032</v>
+        <v>35.7638912</v>
       </c>
       <c r="N87">
-        <v>92.19890677551021</v>
+        <v>91.78304757551021</v>
       </c>
       <c r="O87">
-        <v>13.82983601632653</v>
+        <v>13.76745713632653</v>
       </c>
       <c r="P87">
-        <v>78.36907075918367</v>
+        <v>78.01559043918368</v>
       </c>
       <c r="Q87">
-        <v>113.1690707591837</v>
+        <v>112.8155904391837</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3727280484624174</v>
+        <v>0.3954778512616851</v>
       </c>
       <c r="T87">
-        <v>4.500287644431636</v>
+        <v>4.813447243102687</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.608317961676345</v>
+        <v>3.566360776075457</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1001771991766359</v>
+        <v>0.1001559410839092</v>
       </c>
       <c r="C88">
-        <v>107.3674428866321</v>
+        <v>100.6151560066704</v>
       </c>
       <c r="D88">
-        <v>414.9914428866321</v>
+        <v>415.0231560066703</v>
       </c>
       <c r="E88">
-        <v>242.524</v>
+        <v>249.308</v>
       </c>
       <c r="F88">
-        <v>583.424</v>
+        <v>590.208</v>
       </c>
       <c r="G88">
         <v>275.8</v>
@@ -8491,28 +8491,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M88">
-        <v>35.7638912</v>
+        <v>36.1797504</v>
       </c>
       <c r="N88">
-        <v>91.78304757551021</v>
+        <v>91.36718837551021</v>
       </c>
       <c r="O88">
-        <v>13.76745713632653</v>
+        <v>13.70507825632653</v>
       </c>
       <c r="P88">
-        <v>78.01559043918368</v>
+        <v>77.66211011918368</v>
       </c>
       <c r="Q88">
-        <v>112.8155904391837</v>
+        <v>112.4621101191837</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3954778512616851</v>
+        <v>0.4217276237223785</v>
       </c>
       <c r="T88">
-        <v>4.813447243102687</v>
+        <v>5.174785241569285</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.566360776075457</v>
+        <v>3.525368123476889</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1001559410839092</v>
+        <v>0.1022290829911825</v>
       </c>
       <c r="C89">
-        <v>100.6151560066704</v>
+        <v>90.76105761581925</v>
       </c>
       <c r="D89">
-        <v>415.0231560066703</v>
+        <v>411.9530576158191</v>
       </c>
       <c r="E89">
-        <v>249.308</v>
+        <v>256.092</v>
       </c>
       <c r="F89">
-        <v>590.208</v>
+        <v>596.992</v>
       </c>
       <c r="G89">
         <v>275.8</v>
@@ -8573,45 +8573,45 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M89">
-        <v>36.1797504</v>
+        <v>38.2671872</v>
       </c>
       <c r="N89">
-        <v>91.36718837551021</v>
+        <v>89.2797515755102</v>
       </c>
       <c r="O89">
-        <v>13.70507825632653</v>
+        <v>13.39196273632653</v>
       </c>
       <c r="P89">
-        <v>77.66211011918368</v>
+        <v>75.88778883918367</v>
       </c>
       <c r="Q89">
-        <v>112.4621101191837</v>
+        <v>110.6877888391837</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4217276237223785</v>
+        <v>0.4523523582598544</v>
       </c>
       <c r="T89">
-        <v>5.174785241569285</v>
+        <v>5.596346239780316</v>
       </c>
       <c r="U89">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V89">
         <v>0.15</v>
       </c>
       <c r="W89">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y89">
-        <v>3.525368123476889</v>
+        <v>3.333062817209366</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1022290829911825</v>
+        <v>0.1022316248984558</v>
       </c>
       <c r="C90">
-        <v>90.76105761581925</v>
+        <v>83.97332120664248</v>
       </c>
       <c r="D90">
-        <v>411.9530576158191</v>
+        <v>411.9493212066424</v>
       </c>
       <c r="E90">
-        <v>256.092</v>
+        <v>262.876</v>
       </c>
       <c r="F90">
-        <v>596.992</v>
+        <v>603.776</v>
       </c>
       <c r="G90">
         <v>275.8</v>
@@ -8655,28 +8655,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M90">
-        <v>38.2671872</v>
+        <v>38.7020416</v>
       </c>
       <c r="N90">
-        <v>89.2797515755102</v>
+        <v>88.84489717551021</v>
       </c>
       <c r="O90">
-        <v>13.39196273632653</v>
+        <v>13.32673457632653</v>
       </c>
       <c r="P90">
-        <v>75.88778883918367</v>
+        <v>75.51816259918368</v>
       </c>
       <c r="Q90">
-        <v>110.6877888391837</v>
+        <v>110.3181625991837</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4523523582598544</v>
+        <v>0.4885452263495984</v>
       </c>
       <c r="T90">
-        <v>5.596346239780316</v>
+        <v>6.094554692211534</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.333062817209366</v>
+        <v>3.295612673195778</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1022316248984558</v>
+        <v>0.1022341668057291</v>
       </c>
       <c r="C91">
-        <v>83.97332120664248</v>
+        <v>77.18558486524353</v>
       </c>
       <c r="D91">
-        <v>411.9493212066424</v>
+        <v>411.9455848652434</v>
       </c>
       <c r="E91">
-        <v>262.876</v>
+        <v>269.66</v>
       </c>
       <c r="F91">
-        <v>603.776</v>
+        <v>610.5599999999999</v>
       </c>
       <c r="G91">
         <v>275.8</v>
@@ -8737,28 +8737,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M91">
-        <v>38.7020416</v>
+        <v>39.136896</v>
       </c>
       <c r="N91">
-        <v>88.84489717551021</v>
+        <v>88.41004277551022</v>
       </c>
       <c r="O91">
-        <v>13.32673457632653</v>
+        <v>13.26150641632653</v>
       </c>
       <c r="P91">
-        <v>75.51816259918368</v>
+        <v>75.14853635918368</v>
       </c>
       <c r="Q91">
-        <v>110.3181625991837</v>
+        <v>109.9485363591837</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4885452263495984</v>
+        <v>0.5319766680572914</v>
       </c>
       <c r="T91">
-        <v>6.094554692211534</v>
+        <v>6.692404835128997</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.295612673195778</v>
+        <v>3.258994754604714</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1022341668057291</v>
+        <v>0.1022367087130024</v>
       </c>
       <c r="C92">
-        <v>77.18558486524353</v>
+        <v>70.39784859162023</v>
       </c>
       <c r="D92">
-        <v>411.9455848652434</v>
+        <v>411.9418485916203</v>
       </c>
       <c r="E92">
-        <v>269.66</v>
+        <v>276.4440000000001</v>
       </c>
       <c r="F92">
-        <v>610.5599999999999</v>
+        <v>617.3440000000001</v>
       </c>
       <c r="G92">
         <v>275.8</v>
@@ -8819,28 +8819,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M92">
-        <v>39.136896</v>
+        <v>39.57175040000001</v>
       </c>
       <c r="N92">
-        <v>88.41004277551022</v>
+        <v>87.97518837551021</v>
       </c>
       <c r="O92">
-        <v>13.26150641632653</v>
+        <v>13.19627825632653</v>
       </c>
       <c r="P92">
-        <v>75.14853635918368</v>
+        <v>74.77891011918368</v>
       </c>
       <c r="Q92">
-        <v>109.9485363591837</v>
+        <v>109.5789101191837</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5319766680572914</v>
+        <v>0.5850595412555826</v>
       </c>
       <c r="T92">
-        <v>6.692404835128997</v>
+        <v>7.42311056536145</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.258994754604714</v>
+        <v>3.223181625433233</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1022367087130024</v>
+        <v>0.1022392506202757</v>
       </c>
       <c r="C93">
-        <v>70.39784859162023</v>
+        <v>63.61011238577123</v>
       </c>
       <c r="D93">
-        <v>411.9418485916203</v>
+        <v>411.9381123857712</v>
       </c>
       <c r="E93">
-        <v>276.4440000000001</v>
+        <v>283.2280000000001</v>
       </c>
       <c r="F93">
-        <v>617.3440000000001</v>
+        <v>624.128</v>
       </c>
       <c r="G93">
         <v>275.8</v>
@@ -8901,28 +8901,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M93">
-        <v>39.57175040000001</v>
+        <v>40.00660480000001</v>
       </c>
       <c r="N93">
-        <v>87.97518837551021</v>
+        <v>87.54033397551021</v>
       </c>
       <c r="O93">
-        <v>13.19627825632653</v>
+        <v>13.13105009632653</v>
       </c>
       <c r="P93">
-        <v>74.77891011918368</v>
+        <v>74.40928387918368</v>
       </c>
       <c r="Q93">
-        <v>109.5789101191837</v>
+        <v>109.2092838791837</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5850595412555826</v>
+        <v>0.6514131327534469</v>
       </c>
       <c r="T93">
-        <v>7.42311056536145</v>
+        <v>8.336492728152018</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.223181625433233</v>
+        <v>3.188147042548089</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1022392506202757</v>
+        <v>0.102241792527549</v>
       </c>
       <c r="C94">
-        <v>63.61011238577123</v>
+        <v>56.82237624769436</v>
       </c>
       <c r="D94">
-        <v>411.9381123857712</v>
+        <v>411.9343762476944</v>
       </c>
       <c r="E94">
-        <v>283.2280000000001</v>
+        <v>290.0120000000001</v>
       </c>
       <c r="F94">
-        <v>624.128</v>
+        <v>630.912</v>
       </c>
       <c r="G94">
         <v>275.8</v>
@@ -8983,28 +8983,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M94">
-        <v>40.00660480000001</v>
+        <v>40.4414592</v>
       </c>
       <c r="N94">
-        <v>87.54033397551021</v>
+        <v>87.1054795755102</v>
       </c>
       <c r="O94">
-        <v>13.13105009632653</v>
+        <v>13.06582193632653</v>
       </c>
       <c r="P94">
-        <v>74.40928387918368</v>
+        <v>74.03965763918367</v>
       </c>
       <c r="Q94">
-        <v>109.2092838791837</v>
+        <v>108.8396576391837</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6514131327534469</v>
+        <v>0.7367248932507009</v>
       </c>
       <c r="T94">
-        <v>8.336492728152018</v>
+        <v>9.510841223168462</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.188147042548089</v>
+        <v>3.153865891552948</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.102241792527549</v>
+        <v>0.1022443344348223</v>
       </c>
       <c r="C95">
-        <v>56.82237624769436</v>
+        <v>50.03464017738804</v>
       </c>
       <c r="D95">
-        <v>411.9343762476944</v>
+        <v>411.930640177388</v>
       </c>
       <c r="E95">
-        <v>290.0120000000001</v>
+        <v>296.796</v>
       </c>
       <c r="F95">
-        <v>630.912</v>
+        <v>637.696</v>
       </c>
       <c r="G95">
         <v>275.8</v>
@@ -9065,28 +9065,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M95">
-        <v>40.4414592</v>
+        <v>40.8763136</v>
       </c>
       <c r="N95">
-        <v>87.1054795755102</v>
+        <v>86.67062517551021</v>
       </c>
       <c r="O95">
-        <v>13.06582193632653</v>
+        <v>13.00059377632653</v>
       </c>
       <c r="P95">
-        <v>74.03965763918367</v>
+        <v>73.67003139918369</v>
       </c>
       <c r="Q95">
-        <v>108.8396576391837</v>
+        <v>108.4700313991837</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7367248932507009</v>
+        <v>0.8504739072470395</v>
       </c>
       <c r="T95">
-        <v>9.510841223168462</v>
+        <v>11.07663921652372</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.153865891552948</v>
+        <v>3.120314126749194</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1022443344348223</v>
+        <v>0.1022468763420956</v>
       </c>
       <c r="C96">
-        <v>50.03464017738804</v>
+        <v>43.24690417484999</v>
       </c>
       <c r="D96">
-        <v>411.930640177388</v>
+        <v>411.9269041748501</v>
       </c>
       <c r="E96">
-        <v>296.796</v>
+        <v>303.58</v>
       </c>
       <c r="F96">
-        <v>637.696</v>
+        <v>644.48</v>
       </c>
       <c r="G96">
         <v>275.8</v>
@@ -9147,28 +9147,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M96">
-        <v>40.8763136</v>
+        <v>41.311168</v>
       </c>
       <c r="N96">
-        <v>86.67062517551021</v>
+        <v>86.23577077551022</v>
       </c>
       <c r="O96">
-        <v>13.00059377632653</v>
+        <v>12.93536561632653</v>
       </c>
       <c r="P96">
-        <v>73.67003139918369</v>
+        <v>73.30040515918368</v>
       </c>
       <c r="Q96">
-        <v>108.4700313991837</v>
+        <v>108.1004051591837</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8504739072470395</v>
+        <v>1.009722526841914</v>
       </c>
       <c r="T96">
-        <v>11.07663921652372</v>
+        <v>13.26875640722109</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.120314126749194</v>
+        <v>3.087468714888677</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1022468763420956</v>
+        <v>0.1022494182493689</v>
       </c>
       <c r="C97">
-        <v>43.24690417484999</v>
+        <v>36.45916824007895</v>
       </c>
       <c r="D97">
-        <v>411.9269041748501</v>
+        <v>411.923168240079</v>
       </c>
       <c r="E97">
-        <v>303.58</v>
+        <v>310.364</v>
       </c>
       <c r="F97">
-        <v>644.48</v>
+        <v>651.264</v>
       </c>
       <c r="G97">
         <v>275.8</v>
@@ -9229,28 +9229,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M97">
-        <v>41.311168</v>
+        <v>41.7460224</v>
       </c>
       <c r="N97">
-        <v>86.23577077551022</v>
+        <v>85.80091637551021</v>
       </c>
       <c r="O97">
-        <v>12.93536561632653</v>
+        <v>12.87013745632653</v>
       </c>
       <c r="P97">
-        <v>73.30040515918368</v>
+        <v>72.93077891918368</v>
       </c>
       <c r="Q97">
-        <v>108.1004051591837</v>
+        <v>107.7307789191837</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.009722526841914</v>
+        <v>1.248595456234226</v>
       </c>
       <c r="T97">
-        <v>13.26875640722109</v>
+        <v>16.55693219326714</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.087468714888677</v>
+        <v>3.055307582441919</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1022494182493689</v>
+        <v>0.1022519601566422</v>
       </c>
       <c r="C98">
-        <v>36.45916824007884</v>
+        <v>29.67143237307255</v>
       </c>
       <c r="D98">
-        <v>411.9231682400789</v>
+        <v>411.9194323730726</v>
       </c>
       <c r="E98">
-        <v>310.364</v>
+        <v>317.148</v>
       </c>
       <c r="F98">
-        <v>651.264</v>
+        <v>658.048</v>
       </c>
       <c r="G98">
         <v>275.8</v>
@@ -9311,28 +9311,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M98">
-        <v>41.7460224</v>
+        <v>42.1808768</v>
       </c>
       <c r="N98">
-        <v>85.80091637551021</v>
+        <v>85.36606197551021</v>
       </c>
       <c r="O98">
-        <v>12.87013745632653</v>
+        <v>12.80490929632653</v>
       </c>
       <c r="P98">
-        <v>72.93077891918368</v>
+        <v>72.56115267918368</v>
       </c>
       <c r="Q98">
-        <v>107.7307789191837</v>
+        <v>107.3611526791837</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.248595456234223</v>
+        <v>1.646717005221407</v>
       </c>
       <c r="T98">
-        <v>16.55693219326709</v>
+        <v>22.03722517001049</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.055307582441919</v>
+        <v>3.023809566128085</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1022519601566422</v>
+        <v>0.1087519020639155</v>
       </c>
       <c r="C99">
-        <v>29.67143237307255</v>
+        <v>13.55101185825458</v>
       </c>
       <c r="D99">
-        <v>411.9194323730726</v>
+        <v>402.5830118582546</v>
       </c>
       <c r="E99">
-        <v>317.148</v>
+        <v>323.932</v>
       </c>
       <c r="F99">
-        <v>658.048</v>
+        <v>664.832</v>
       </c>
       <c r="G99">
         <v>275.8</v>
@@ -9393,45 +9393,45 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M99">
-        <v>42.1808768</v>
+        <v>47.8014208</v>
       </c>
       <c r="N99">
-        <v>85.36606197551021</v>
+        <v>79.74551797551021</v>
       </c>
       <c r="O99">
-        <v>12.80490929632653</v>
+        <v>11.96182769632653</v>
       </c>
       <c r="P99">
-        <v>72.56115267918368</v>
+        <v>67.78369027918367</v>
       </c>
       <c r="Q99">
-        <v>107.3611526791837</v>
+        <v>102.5836902791837</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.646717005221407</v>
+        <v>2.442960103195775</v>
       </c>
       <c r="T99">
-        <v>22.03722517001049</v>
+        <v>32.99781112349727</v>
       </c>
       <c r="U99">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V99">
         <v>0.15</v>
       </c>
       <c r="W99">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y99">
-        <v>3.023809566128085</v>
+        <v>2.668266688330532</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1087519020639155</v>
+        <v>0.1088207439711888</v>
       </c>
       <c r="C100">
-        <v>13.55101185825458</v>
+        <v>6.670392812243335</v>
       </c>
       <c r="D100">
-        <v>402.5830118582546</v>
+        <v>402.4863928122433</v>
       </c>
       <c r="E100">
-        <v>323.932</v>
+        <v>330.716</v>
       </c>
       <c r="F100">
-        <v>664.832</v>
+        <v>671.616</v>
       </c>
       <c r="G100">
         <v>275.8</v>
@@ -9475,28 +9475,28 @@
         <v>127.5469387755102</v>
       </c>
       <c r="M100">
-        <v>47.8014208</v>
+        <v>48.2891904</v>
       </c>
       <c r="N100">
-        <v>79.74551797551021</v>
+        <v>79.2577483755102</v>
       </c>
       <c r="O100">
-        <v>11.96182769632653</v>
+        <v>11.88866225632653</v>
       </c>
       <c r="P100">
-        <v>67.78369027918367</v>
+        <v>67.36908611918368</v>
       </c>
       <c r="Q100">
-        <v>102.5836902791837</v>
+        <v>102.1690861191837</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.442960103195775</v>
+        <v>4.83168939711888</v>
       </c>
       <c r="T100">
-        <v>32.99781112349727</v>
+        <v>65.87956898395763</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.668266688330532</v>
+        <v>2.641314499559516</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1088207439711888</v>
-      </c>
-      <c r="C101">
-        <v>6.670392812243335</v>
-      </c>
-      <c r="D101">
-        <v>402.4863928122433</v>
-      </c>
-      <c r="E101">
-        <v>330.716</v>
-      </c>
-      <c r="F101">
-        <v>671.616</v>
-      </c>
-      <c r="G101">
-        <v>275.8</v>
-      </c>
-      <c r="H101">
-        <v>337.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>162.3469387755102</v>
-      </c>
-      <c r="K101">
-        <v>34.8</v>
-      </c>
-      <c r="L101">
-        <v>127.5469387755102</v>
-      </c>
-      <c r="M101">
-        <v>48.2891904</v>
-      </c>
-      <c r="N101">
-        <v>79.2577483755102</v>
-      </c>
-      <c r="O101">
-        <v>11.88866225632653</v>
-      </c>
-      <c r="P101">
-        <v>67.36908611918368</v>
-      </c>
-      <c r="Q101">
-        <v>102.1690861191837</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.83168939711888</v>
-      </c>
-      <c r="T101">
-        <v>65.87956898395763</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.061115</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.641314499559516</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
